--- a/pipeline/lead-tracker.xlsx
+++ b/pipeline/lead-tracker.xlsx
@@ -102,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -122,6 +122,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -488,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q66"/>
+  <dimension ref="A1:Q75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -679,43 +688,43 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="5" t="inlineStr"/>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr"/>
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Tiling Experts</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>Trades &amp; Home Services</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>KwaZulu-Natal</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>La Lucia</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>082 753 0350</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="G5" s="9" t="inlineStr"/>
+      <c r="H5" s="9" t="inlineStr"/>
+      <c r="I5" s="9" t="inlineStr"/>
+      <c r="J5" s="9" t="inlineStr"/>
+      <c r="K5" s="9" t="inlineStr"/>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M5" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -725,12 +734,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O5" s="5" t="inlineStr">
+      <c r="O5" s="9" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr"/>
+      <c r="P5" s="9" t="inlineStr"/>
       <c r="Q5" s="7" t="inlineStr">
         <is>
           <t>4.8 stars | 23 reviews | Monday: 7:30 AM – 4:00 PM | Tuesday: 7:30 AM – 4:00 PM | Wednesday: 7:30 AM – 4:00 PM | https://maps.google.com/?cid=8098614939933451806&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -738,43 +747,43 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="5" t="inlineStr"/>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr"/>
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Beauty Kingdom</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Beauty &amp; Wellness</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>KwaZulu-Natal</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Chatsworth</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>031 401 8659</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M6" s="5" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr"/>
+      <c r="H6" s="9" t="inlineStr"/>
+      <c r="I6" s="9" t="inlineStr"/>
+      <c r="J6" s="9" t="inlineStr"/>
+      <c r="K6" s="9" t="inlineStr"/>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M6" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -784,12 +793,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O6" s="5" t="inlineStr">
+      <c r="O6" s="9" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="P6" s="5" t="inlineStr"/>
+      <c r="P6" s="9" t="inlineStr"/>
       <c r="Q6" s="7" t="inlineStr">
         <is>
           <t>4.6 stars | 341 reviews | Monday: 9:00 AM – 6:00 PM | Tuesday: 9:00 AM – 6:00 PM | Wednesday: 9:00 AM – 6:00 PM | https://maps.google.com/?cid=5902211889831189732&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -797,43 +806,43 @@
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="5" t="inlineStr"/>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr"/>
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>HALEY’S BEAUTY THERAPY</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>Beauty &amp; Wellness</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>KwaZulu-Natal</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>Chatsworth</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>081 267 4248</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr"/>
-      <c r="J7" s="5" t="inlineStr"/>
-      <c r="K7" s="5" t="inlineStr"/>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr"/>
+      <c r="H7" s="9" t="inlineStr"/>
+      <c r="I7" s="9" t="inlineStr"/>
+      <c r="J7" s="9" t="inlineStr"/>
+      <c r="K7" s="9" t="inlineStr"/>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M7" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -843,12 +852,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O7" s="5" t="inlineStr">
+      <c r="O7" s="9" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="P7" s="5" t="inlineStr"/>
+      <c r="P7" s="9" t="inlineStr"/>
       <c r="Q7" s="7" t="inlineStr">
         <is>
           <t>4.8 stars | 146 reviews | Monday: 12:00 – 6:00 PM | Tuesday: 10:00 AM – 6:00 PM | Wednesday: 10:00 AM – 6:00 PM | https://maps.google.com/?cid=7212798743767500606&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -856,43 +865,43 @@
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="5" t="inlineStr"/>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr"/>
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>The Beauty Vault Sanctuary Spa</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Beauty &amp; Wellness</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>KwaZulu-Natal</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>Chatsworth</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>084 923 5216</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr"/>
-      <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr"/>
-      <c r="J8" s="5" t="inlineStr"/>
-      <c r="K8" s="5" t="inlineStr"/>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="inlineStr">
+      <c r="G8" s="9" t="inlineStr"/>
+      <c r="H8" s="9" t="inlineStr"/>
+      <c r="I8" s="9" t="inlineStr"/>
+      <c r="J8" s="9" t="inlineStr"/>
+      <c r="K8" s="9" t="inlineStr"/>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M8" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -902,12 +911,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O8" s="5" t="inlineStr">
+      <c r="O8" s="9" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="P8" s="5" t="inlineStr"/>
+      <c r="P8" s="9" t="inlineStr"/>
       <c r="Q8" s="7" t="inlineStr">
         <is>
           <t>Monday: 7:00 AM – 8:00 PM | Tuesday: 7:00 AM – 8:00 PM | Wednesday: 7:00 AM – 8:00 PM | https://maps.google.com/?cid=5897106547258168965&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -915,43 +924,43 @@
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="5" t="inlineStr"/>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr"/>
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>THE GLAM STUDIO</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>Beauty &amp; Wellness</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>KwaZulu-Natal</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>Chatsworth</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>079 882 6161</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr"/>
-      <c r="H9" s="5" t="inlineStr"/>
-      <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="5" t="inlineStr"/>
-      <c r="K9" s="5" t="inlineStr"/>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr"/>
+      <c r="H9" s="9" t="inlineStr"/>
+      <c r="I9" s="9" t="inlineStr"/>
+      <c r="J9" s="9" t="inlineStr"/>
+      <c r="K9" s="9" t="inlineStr"/>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M9" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -961,12 +970,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O9" s="5" t="inlineStr">
+      <c r="O9" s="9" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="P9" s="5" t="inlineStr"/>
+      <c r="P9" s="9" t="inlineStr"/>
       <c r="Q9" s="7" t="inlineStr">
         <is>
           <t>4.6 stars | 23 reviews | Monday: Closed | Tuesday: 8:30 AM – 5:00 PM | Wednesday: 8:30 AM – 5:00 PM | https://maps.google.com/?cid=5935282822695831857&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -974,43 +983,43 @@
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="5" t="inlineStr"/>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr"/>
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>Pearl's Beauty Lab</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Beauty &amp; Wellness</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>KwaZulu-Natal</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>Chatsworth</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>073 606 9534</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="inlineStr">
+      <c r="G10" s="9" t="inlineStr"/>
+      <c r="H10" s="9" t="inlineStr"/>
+      <c r="I10" s="9" t="inlineStr"/>
+      <c r="J10" s="9" t="inlineStr"/>
+      <c r="K10" s="9" t="inlineStr"/>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M10" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -1020,12 +1029,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O10" s="5" t="inlineStr">
+      <c r="O10" s="9" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="P10" s="5" t="inlineStr"/>
+      <c r="P10" s="9" t="inlineStr"/>
       <c r="Q10" s="7" t="inlineStr">
         <is>
           <t>5 stars | 16 reviews | Monday: 9:00 AM – 5:00 PM | Tuesday: 9:00 AM – 5:00 PM | Wednesday: 9:00 AM – 5:00 PM | https://maps.google.com/?cid=10237563139231933977&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -1033,43 +1042,43 @@
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="5" t="inlineStr"/>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr"/>
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Rejuvenation Retreat</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>Beauty &amp; Wellness</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>KwaZulu-Natal</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>Chatsworth</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>071 365 0275</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M11" s="5" t="inlineStr">
+      <c r="G11" s="9" t="inlineStr"/>
+      <c r="H11" s="9" t="inlineStr"/>
+      <c r="I11" s="9" t="inlineStr"/>
+      <c r="J11" s="9" t="inlineStr"/>
+      <c r="K11" s="9" t="inlineStr"/>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M11" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -1079,12 +1088,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O11" s="5" t="inlineStr">
+      <c r="O11" s="9" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="P11" s="5" t="inlineStr"/>
+      <c r="P11" s="9" t="inlineStr"/>
       <c r="Q11" s="7" t="inlineStr">
         <is>
           <t>5 stars | 1 reviews | Monday: 9:00 AM – 6:00 PM | Tuesday: 9:00 AM – 6:00 PM | Wednesday: 9:00 AM – 6:00 PM | https://maps.google.com/?cid=4407304906041593885&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -1092,43 +1101,43 @@
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="5" t="inlineStr"/>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr"/>
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>The Nail Hive &amp; Beauty</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Beauty &amp; Wellness</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>KwaZulu-Natal</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Chatsworth</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>081 215 1786</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M12" s="5" t="inlineStr">
+      <c r="G12" s="9" t="inlineStr"/>
+      <c r="H12" s="9" t="inlineStr"/>
+      <c r="I12" s="9" t="inlineStr"/>
+      <c r="J12" s="9" t="inlineStr"/>
+      <c r="K12" s="9" t="inlineStr"/>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M12" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -1138,12 +1147,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O12" s="5" t="inlineStr">
+      <c r="O12" s="9" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="P12" s="5" t="inlineStr"/>
+      <c r="P12" s="9" t="inlineStr"/>
       <c r="Q12" s="7" t="inlineStr">
         <is>
           <t>5 stars | 16 reviews | Monday: 9:00 AM – 5:00 PM | Tuesday: 9:00 AM – 5:00 PM | Wednesday: 9:00 AM – 5:00 PM | https://maps.google.com/?cid=12886772067834600651&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -1151,43 +1160,43 @@
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="5" t="inlineStr"/>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr"/>
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Thee Beauty Hideout</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>Beauty &amp; Wellness</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>KwaZulu-Natal</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>Chatsworth</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>081 259 5141</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr"/>
-      <c r="H13" s="5" t="inlineStr"/>
-      <c r="I13" s="5" t="inlineStr"/>
-      <c r="J13" s="5" t="inlineStr"/>
-      <c r="K13" s="5" t="inlineStr"/>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M13" s="5" t="inlineStr">
+      <c r="G13" s="9" t="inlineStr"/>
+      <c r="H13" s="9" t="inlineStr"/>
+      <c r="I13" s="9" t="inlineStr"/>
+      <c r="J13" s="9" t="inlineStr"/>
+      <c r="K13" s="9" t="inlineStr"/>
+      <c r="L13" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M13" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -1197,12 +1206,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O13" s="5" t="inlineStr">
+      <c r="O13" s="9" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="P13" s="5" t="inlineStr"/>
+      <c r="P13" s="9" t="inlineStr"/>
       <c r="Q13" s="7" t="inlineStr">
         <is>
           <t>4 stars | 3 reviews | Monday: 9:00 AM – 5:30 PM | Tuesday: 9:00 AM – 5:30 PM | Wednesday: 9:00 AM – 5:30 PM | https://maps.google.com/?cid=12514477215559661852&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -1210,43 +1219,43 @@
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="5" t="inlineStr"/>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr"/>
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>La Tierra Spa &amp; Aesthetics</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Beauty &amp; Wellness</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>KwaZulu-Natal</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>Chatsworth</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t>084 722 6900</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr"/>
-      <c r="H14" s="5" t="inlineStr"/>
-      <c r="I14" s="5" t="inlineStr"/>
-      <c r="J14" s="5" t="inlineStr"/>
-      <c r="K14" s="5" t="inlineStr"/>
-      <c r="L14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M14" s="5" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr"/>
+      <c r="H14" s="9" t="inlineStr"/>
+      <c r="I14" s="9" t="inlineStr"/>
+      <c r="J14" s="9" t="inlineStr"/>
+      <c r="K14" s="9" t="inlineStr"/>
+      <c r="L14" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M14" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -1256,12 +1265,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O14" s="5" t="inlineStr">
+      <c r="O14" s="9" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="P14" s="5" t="inlineStr"/>
+      <c r="P14" s="9" t="inlineStr"/>
       <c r="Q14" s="7" t="inlineStr">
         <is>
           <t>4.8 stars | 65 reviews | Monday: Closed | Tuesday: 8:00 AM – 5:00 PM | Wednesday: 8:00 AM – 5:00 PM | https://maps.google.com/?cid=3785612442891382587&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -1269,43 +1278,43 @@
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="5" t="inlineStr"/>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr"/>
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>CHARLOTTES HEALTH AND BEAUTY</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Beauty &amp; Wellness</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>KwaZulu-Natal</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>Chatsworth</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t>031 401 9350</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr"/>
-      <c r="H15" s="5" t="inlineStr"/>
-      <c r="I15" s="5" t="inlineStr"/>
-      <c r="J15" s="5" t="inlineStr"/>
-      <c r="K15" s="5" t="inlineStr"/>
-      <c r="L15" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M15" s="5" t="inlineStr">
+      <c r="G15" s="9" t="inlineStr"/>
+      <c r="H15" s="9" t="inlineStr"/>
+      <c r="I15" s="9" t="inlineStr"/>
+      <c r="J15" s="9" t="inlineStr"/>
+      <c r="K15" s="9" t="inlineStr"/>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M15" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -1315,12 +1324,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O15" s="5" t="inlineStr">
+      <c r="O15" s="9" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="P15" s="5" t="inlineStr"/>
+      <c r="P15" s="9" t="inlineStr"/>
       <c r="Q15" s="7" t="inlineStr">
         <is>
           <t>4.9 stars | 26 reviews | Monday: 8:00 AM – 5:00 PM | Tuesday: 8:00 AM – 5:00 PM | Wednesday: 8:00 AM – 5:00 PM | https://maps.google.com/?cid=14208271565492437224&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -1328,43 +1337,43 @@
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="5" t="inlineStr"/>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr"/>
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>AD Hair Nails &amp; Beauty Spa</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>Beauty &amp; Wellness</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>KwaZulu-Natal</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>Chatsworth</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" s="9" t="inlineStr">
         <is>
           <t>031 002 7403</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M16" s="5" t="inlineStr">
+      <c r="G16" s="9" t="inlineStr"/>
+      <c r="H16" s="9" t="inlineStr"/>
+      <c r="I16" s="9" t="inlineStr"/>
+      <c r="J16" s="9" t="inlineStr"/>
+      <c r="K16" s="9" t="inlineStr"/>
+      <c r="L16" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M16" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -1374,12 +1383,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O16" s="5" t="inlineStr">
+      <c r="O16" s="9" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="P16" s="5" t="inlineStr"/>
+      <c r="P16" s="9" t="inlineStr"/>
       <c r="Q16" s="7" t="inlineStr">
         <is>
           <t>5 stars | 9 reviews | Monday: 9:00 AM – 5:00 PM | Tuesday: 9:00 AM – 5:00 PM | Wednesday: 9:00 AM – 5:00 PM | https://maps.google.com/?cid=4077210597883238985&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -1387,43 +1396,43 @@
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="5" t="inlineStr"/>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr"/>
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>Juanitashealth&amp;beauty</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>Beauty &amp; Wellness</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>KwaZulu-Natal</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>Chatsworth</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>083 682 4604</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M17" s="5" t="inlineStr">
+      <c r="G17" s="9" t="inlineStr"/>
+      <c r="H17" s="9" t="inlineStr"/>
+      <c r="I17" s="9" t="inlineStr"/>
+      <c r="J17" s="9" t="inlineStr"/>
+      <c r="K17" s="9" t="inlineStr"/>
+      <c r="L17" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M17" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -1433,12 +1442,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O17" s="5" t="inlineStr">
+      <c r="O17" s="9" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="P17" s="5" t="inlineStr"/>
+      <c r="P17" s="9" t="inlineStr"/>
       <c r="Q17" s="7" t="inlineStr">
         <is>
           <t>4.6 stars | 9 reviews | Monday: Closed | Tuesday: Closed | Wednesday: 9:00 AM – 5:00 PM | https://maps.google.com/?cid=901754277589383452&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -1446,43 +1455,43 @@
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="5" t="inlineStr"/>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr"/>
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>Crystal Spa and Aesthetics</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>Beauty &amp; Wellness</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>KwaZulu-Natal</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>Chatsworth</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" s="9" t="inlineStr">
         <is>
           <t>069 993 1620</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
-      <c r="L18" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M18" s="5" t="inlineStr">
+      <c r="G18" s="9" t="inlineStr"/>
+      <c r="H18" s="9" t="inlineStr"/>
+      <c r="I18" s="9" t="inlineStr"/>
+      <c r="J18" s="9" t="inlineStr"/>
+      <c r="K18" s="9" t="inlineStr"/>
+      <c r="L18" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M18" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -1492,12 +1501,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O18" s="5" t="inlineStr">
+      <c r="O18" s="9" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="P18" s="5" t="inlineStr"/>
+      <c r="P18" s="9" t="inlineStr"/>
       <c r="Q18" s="7" t="inlineStr">
         <is>
           <t>4 stars | 4 reviews | Monday: 8:00 AM – 7:00 PM | Tuesday: 8:00 AM – 7:00 PM | Wednesday: 8:00 AM – 7:00 PM | https://maps.google.com/?cid=2183555200601980177&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -1505,43 +1514,43 @@
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="5" t="inlineStr"/>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr"/>
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>Le' beautè Salon</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>Beauty &amp; Wellness</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>KwaZulu-Natal</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>Chatsworth</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="9" t="inlineStr">
         <is>
           <t>082 321 5631</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr"/>
-      <c r="H19" s="5" t="inlineStr"/>
-      <c r="I19" s="5" t="inlineStr"/>
-      <c r="J19" s="5" t="inlineStr"/>
-      <c r="K19" s="5" t="inlineStr"/>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M19" s="5" t="inlineStr">
+      <c r="G19" s="9" t="inlineStr"/>
+      <c r="H19" s="9" t="inlineStr"/>
+      <c r="I19" s="9" t="inlineStr"/>
+      <c r="J19" s="9" t="inlineStr"/>
+      <c r="K19" s="9" t="inlineStr"/>
+      <c r="L19" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M19" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -1551,12 +1560,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O19" s="5" t="inlineStr">
+      <c r="O19" s="9" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="P19" s="5" t="inlineStr"/>
+      <c r="P19" s="9" t="inlineStr"/>
       <c r="Q19" s="7" t="inlineStr">
         <is>
           <t>Monday: 9:00 AM – 5:00 PM | Tuesday: 9:00 AM – 5:00 PM | Wednesday: 9:00 AM – 5:00 PM | https://maps.google.com/?cid=1658288402048617539&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -1564,43 +1573,43 @@
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="5" t="inlineStr"/>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr"/>
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>Graham's Appliances &amp; Refrigeration</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>Trades &amp; Home Services</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>Western Cape</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>Strand</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F20" s="9" t="inlineStr">
         <is>
           <t>021 853 1163</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr"/>
-      <c r="H20" s="5" t="inlineStr"/>
-      <c r="I20" s="5" t="inlineStr"/>
-      <c r="J20" s="5" t="inlineStr"/>
-      <c r="K20" s="5" t="inlineStr"/>
-      <c r="L20" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M20" s="5" t="inlineStr">
+      <c r="G20" s="9" t="inlineStr"/>
+      <c r="H20" s="9" t="inlineStr"/>
+      <c r="I20" s="9" t="inlineStr"/>
+      <c r="J20" s="9" t="inlineStr"/>
+      <c r="K20" s="9" t="inlineStr"/>
+      <c r="L20" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M20" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -1610,12 +1619,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O20" s="5" t="inlineStr">
+      <c r="O20" s="9" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="P20" s="5" t="inlineStr"/>
+      <c r="P20" s="9" t="inlineStr"/>
       <c r="Q20" s="7" t="inlineStr">
         <is>
           <t>3.7 stars | 256 reviews | Monday: 8:00 AM – 5:00 PM | Tuesday: 8:00 AM – 5:00 PM | Wednesday: 8:00 AM – 5:00 PM | https://maps.google.com/?cid=10690443470884824657&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -1623,43 +1632,43 @@
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="5" t="inlineStr"/>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr"/>
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>ARS Air-Conditioning &amp; Refrigeration services</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>Trades &amp; Home Services</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>Western Cape</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>Strand</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F21" s="9" t="inlineStr">
         <is>
           <t>082 367 6000</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr"/>
-      <c r="H21" s="5" t="inlineStr"/>
-      <c r="I21" s="5" t="inlineStr"/>
-      <c r="J21" s="5" t="inlineStr"/>
-      <c r="K21" s="5" t="inlineStr"/>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr"/>
+      <c r="H21" s="9" t="inlineStr"/>
+      <c r="I21" s="9" t="inlineStr"/>
+      <c r="J21" s="9" t="inlineStr"/>
+      <c r="K21" s="9" t="inlineStr"/>
+      <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M21" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -1669,12 +1678,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O21" s="5" t="inlineStr">
+      <c r="O21" s="9" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="P21" s="5" t="inlineStr"/>
+      <c r="P21" s="9" t="inlineStr"/>
       <c r="Q21" s="7" t="inlineStr">
         <is>
           <t>5 stars | 2 reviews | Monday: 8:00 AM – 5:00 PM | Tuesday: 8:00 AM – 5:00 PM | Wednesday: 8:00 AM – 5:00 PM | https://maps.google.com/?cid=16057294301577441192&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -1682,43 +1691,43 @@
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="5" t="inlineStr"/>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr"/>
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>MOBILE CAR AIRCON REGAS &amp; BATTERIES</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>Trades &amp; Home Services</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>Western Cape</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>Strand</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F22" s="9" t="inlineStr">
         <is>
           <t>064 408 4632</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M22" s="5" t="inlineStr">
+      <c r="G22" s="9" t="inlineStr"/>
+      <c r="H22" s="9" t="inlineStr"/>
+      <c r="I22" s="9" t="inlineStr"/>
+      <c r="J22" s="9" t="inlineStr"/>
+      <c r="K22" s="9" t="inlineStr"/>
+      <c r="L22" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M22" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -1728,12 +1737,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O22" s="5" t="inlineStr">
+      <c r="O22" s="9" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="P22" s="5" t="inlineStr"/>
+      <c r="P22" s="9" t="inlineStr"/>
       <c r="Q22" s="7" t="inlineStr">
         <is>
           <t>5 stars | 12 reviews | Monday: 8:00 AM – 8:00 PM | Tuesday: 8:00 AM – 8:00 PM | Wednesday: 8:00 AM – 8:00 PM | https://maps.google.com/?cid=18243218095361922341&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -1741,43 +1750,43 @@
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="5" t="inlineStr"/>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr"/>
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>Nick &amp; Ethan Pest Control</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>Trades &amp; Home Services</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>Western Cape</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>Fish Hoek</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F23" s="9" t="inlineStr">
         <is>
           <t>074 356 6279</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
+      <c r="G23" s="9" t="inlineStr"/>
+      <c r="H23" s="9" t="inlineStr"/>
+      <c r="I23" s="9" t="inlineStr"/>
+      <c r="J23" s="9" t="inlineStr"/>
+      <c r="K23" s="9" t="inlineStr"/>
+      <c r="L23" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M23" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -1787,12 +1796,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O23" s="5" t="inlineStr">
+      <c r="O23" s="9" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="P23" s="5" t="inlineStr"/>
+      <c r="P23" s="9" t="inlineStr"/>
       <c r="Q23" s="7" t="inlineStr">
         <is>
           <t>4.9 stars | 56 reviews | Monday: Open 24 hours | Tuesday: Open 24 hours | Wednesday: Open 24 hours | https://maps.google.com/?cid=7832124028168743916&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -1800,43 +1809,43 @@
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="5" t="inlineStr"/>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr"/>
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>King's Kid Creche</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>Professional Services</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>Western Cape</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>Gardens</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F24" s="9" t="inlineStr">
         <is>
           <t>012 753 3527</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
-      <c r="L24" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M24" s="5" t="inlineStr">
+      <c r="G24" s="9" t="inlineStr"/>
+      <c r="H24" s="9" t="inlineStr"/>
+      <c r="I24" s="9" t="inlineStr"/>
+      <c r="J24" s="9" t="inlineStr"/>
+      <c r="K24" s="9" t="inlineStr"/>
+      <c r="L24" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M24" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -1846,12 +1855,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O24" s="5" t="inlineStr">
+      <c r="O24" s="9" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="P24" s="5" t="inlineStr"/>
+      <c r="P24" s="9" t="inlineStr"/>
       <c r="Q24" s="7" t="inlineStr">
         <is>
           <t>4.8 stars | 9 reviews | Monday: 6:30 AM – 5:30 PM | Tuesday: 6:30 AM – 5:30 PM | Wednesday: 6:30 AM – 5:30 PM | https://maps.google.com/?cid=7241707342309437473&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -1859,43 +1868,43 @@
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="5" t="inlineStr"/>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr"/>
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>Handyman Services and building renovators</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>Trades &amp; Home Services</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>Gauteng</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E25" s="9" t="inlineStr">
         <is>
           <t>Fourways</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F25" s="9" t="inlineStr">
         <is>
           <t>083 645 4329</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr"/>
-      <c r="H25" s="5" t="inlineStr"/>
-      <c r="I25" s="5" t="inlineStr"/>
-      <c r="J25" s="5" t="inlineStr"/>
-      <c r="K25" s="5" t="inlineStr"/>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
+      <c r="G25" s="9" t="inlineStr"/>
+      <c r="H25" s="9" t="inlineStr"/>
+      <c r="I25" s="9" t="inlineStr"/>
+      <c r="J25" s="9" t="inlineStr"/>
+      <c r="K25" s="9" t="inlineStr"/>
+      <c r="L25" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M25" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -1905,12 +1914,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O25" s="5" t="inlineStr">
+      <c r="O25" s="9" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="P25" s="5" t="inlineStr"/>
+      <c r="P25" s="9" t="inlineStr"/>
       <c r="Q25" s="7" t="inlineStr">
         <is>
           <t>5 stars | 3 reviews | Monday: 7:00 AM – 10:00 PM | Tuesday: 7:00 AM – 10:00 PM | Wednesday: 7:00 AM – 10:00 PM | https://maps.google.com/?cid=10579546401697342776&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -1918,43 +1927,43 @@
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="5" t="inlineStr"/>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr"/>
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>PureSkill Handyman Services</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>Trades &amp; Home Services</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>Gauteng</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>Fourways</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F26" s="9" t="inlineStr">
         <is>
           <t>084 435 9864</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr"/>
-      <c r="H26" s="5" t="inlineStr"/>
-      <c r="I26" s="5" t="inlineStr"/>
-      <c r="J26" s="5" t="inlineStr"/>
-      <c r="K26" s="5" t="inlineStr"/>
-      <c r="L26" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M26" s="5" t="inlineStr">
+      <c r="G26" s="9" t="inlineStr"/>
+      <c r="H26" s="9" t="inlineStr"/>
+      <c r="I26" s="9" t="inlineStr"/>
+      <c r="J26" s="9" t="inlineStr"/>
+      <c r="K26" s="9" t="inlineStr"/>
+      <c r="L26" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M26" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -1964,12 +1973,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O26" s="5" t="inlineStr">
+      <c r="O26" s="9" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="P26" s="5" t="inlineStr"/>
+      <c r="P26" s="9" t="inlineStr"/>
       <c r="Q26" s="7" t="inlineStr">
         <is>
           <t>4.5 stars | 2 reviews | Monday: Open 24 hours | Tuesday: Open 24 hours | Wednesday: Open 24 hours | https://maps.google.com/?cid=16363898909164060442&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -1977,43 +1986,43 @@
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="5" t="inlineStr"/>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr"/>
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>Stark Property Maintenance Pty Ltd</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>Trades &amp; Home Services</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>Gauteng</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>Fourways</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F27" s="9" t="inlineStr">
         <is>
           <t>060 278 4717</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr"/>
-      <c r="H27" s="5" t="inlineStr"/>
-      <c r="I27" s="5" t="inlineStr"/>
-      <c r="J27" s="5" t="inlineStr"/>
-      <c r="K27" s="5" t="inlineStr"/>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
+      <c r="G27" s="9" t="inlineStr"/>
+      <c r="H27" s="9" t="inlineStr"/>
+      <c r="I27" s="9" t="inlineStr"/>
+      <c r="J27" s="9" t="inlineStr"/>
+      <c r="K27" s="9" t="inlineStr"/>
+      <c r="L27" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M27" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -2023,12 +2032,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O27" s="5" t="inlineStr">
+      <c r="O27" s="9" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="P27" s="5" t="inlineStr"/>
+      <c r="P27" s="9" t="inlineStr"/>
       <c r="Q27" s="7" t="inlineStr">
         <is>
           <t>4.9 stars | 38 reviews | Monday: 8:00 AM – 6:00 PM | Tuesday: 8:00 AM – 6:00 PM | Wednesday: 8:00 AM – 6:00 PM | https://maps.google.com/?cid=1126306609276102971&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -2036,43 +2045,43 @@
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="5" t="inlineStr"/>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr"/>
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>Lp handyman services</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>Trades &amp; Home Services</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>Gauteng</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E28" s="9" t="inlineStr">
         <is>
           <t>Fourways</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F28" s="9" t="inlineStr">
         <is>
           <t>064 506 8167</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
-      <c r="L28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M28" s="5" t="inlineStr">
+      <c r="G28" s="9" t="inlineStr"/>
+      <c r="H28" s="9" t="inlineStr"/>
+      <c r="I28" s="9" t="inlineStr"/>
+      <c r="J28" s="9" t="inlineStr"/>
+      <c r="K28" s="9" t="inlineStr"/>
+      <c r="L28" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M28" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -2082,12 +2091,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O28" s="5" t="inlineStr">
+      <c r="O28" s="9" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="P28" s="5" t="inlineStr"/>
+      <c r="P28" s="9" t="inlineStr"/>
       <c r="Q28" s="7" t="inlineStr">
         <is>
           <t>5 stars | 1 reviews | Monday: Open 24 hours | Tuesday: Open 24 hours | Wednesday: Open 24 hours | https://maps.google.com/?cid=6697354469424328163&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -2095,43 +2104,43 @@
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="5" t="inlineStr"/>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr"/>
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>SPJ HANDYMANSERVICES</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>Trades &amp; Home Services</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>Gauteng</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>Fourways</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F29" s="9" t="inlineStr">
         <is>
           <t>067 864 0570</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M29" s="5" t="inlineStr">
+      <c r="G29" s="9" t="inlineStr"/>
+      <c r="H29" s="9" t="inlineStr"/>
+      <c r="I29" s="9" t="inlineStr"/>
+      <c r="J29" s="9" t="inlineStr"/>
+      <c r="K29" s="9" t="inlineStr"/>
+      <c r="L29" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M29" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -2141,12 +2150,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O29" s="5" t="inlineStr">
+      <c r="O29" s="9" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="P29" s="5" t="inlineStr"/>
+      <c r="P29" s="9" t="inlineStr"/>
       <c r="Q29" s="7" t="inlineStr">
         <is>
           <t>5 stars | 1 reviews | Monday: Open 24 hours | Tuesday: Open 24 hours | Wednesday: Open 24 hours | https://maps.google.com/?cid=17489594083991308585&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -2154,43 +2163,43 @@
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="5" t="inlineStr"/>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr"/>
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>Jayden Handyman</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>Trades &amp; Home Services</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>Gauteng</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>Fourways</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F30" s="9" t="inlineStr">
         <is>
           <t>068 662 2533</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
-      <c r="L30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M30" s="5" t="inlineStr">
+      <c r="G30" s="9" t="inlineStr"/>
+      <c r="H30" s="9" t="inlineStr"/>
+      <c r="I30" s="9" t="inlineStr"/>
+      <c r="J30" s="9" t="inlineStr"/>
+      <c r="K30" s="9" t="inlineStr"/>
+      <c r="L30" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M30" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -2200,12 +2209,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O30" s="5" t="inlineStr">
+      <c r="O30" s="9" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="P30" s="5" t="inlineStr"/>
+      <c r="P30" s="9" t="inlineStr"/>
       <c r="Q30" s="7" t="inlineStr">
         <is>
           <t>4.9 stars | 12 reviews | https://maps.google.com/?cid=16758636031194280299&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -2213,43 +2222,43 @@
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="5" t="inlineStr"/>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr"/>
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>At Your Place Catering</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>Food &amp; Hospitality</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>Gauteng</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E31" s="9" t="inlineStr">
         <is>
           <t>Menlyn</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F31" s="9" t="inlineStr">
         <is>
           <t>084 503 8661</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr"/>
-      <c r="H31" s="5" t="inlineStr"/>
-      <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="5" t="inlineStr"/>
-      <c r="K31" s="5" t="inlineStr"/>
-      <c r="L31" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M31" s="5" t="inlineStr">
+      <c r="G31" s="9" t="inlineStr"/>
+      <c r="H31" s="9" t="inlineStr"/>
+      <c r="I31" s="9" t="inlineStr"/>
+      <c r="J31" s="9" t="inlineStr"/>
+      <c r="K31" s="9" t="inlineStr"/>
+      <c r="L31" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M31" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -2259,12 +2268,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O31" s="5" t="inlineStr">
+      <c r="O31" s="9" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="P31" s="5" t="inlineStr"/>
+      <c r="P31" s="9" t="inlineStr"/>
       <c r="Q31" s="7" t="inlineStr">
         <is>
           <t>5 stars | 1 reviews | Monday: 8:00 AM – 5:00 PM | Tuesday: 8:00 AM – 5:00 PM | Wednesday: 8:00 AM – 5:00 PM | https://maps.google.com/?cid=11214900659229279853&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -2272,39 +2281,39 @@
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="5" t="inlineStr"/>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="A32" s="9" t="inlineStr"/>
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>Soulfood catering</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>Food &amp; Hospitality</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D32" s="9" t="inlineStr">
         <is>
           <t>Gauteng</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E32" s="9" t="inlineStr">
         <is>
           <t>Menlyn</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr"/>
-      <c r="G32" s="5" t="inlineStr"/>
-      <c r="H32" s="5" t="inlineStr"/>
-      <c r="I32" s="5" t="inlineStr"/>
-      <c r="J32" s="5" t="inlineStr"/>
-      <c r="K32" s="5" t="inlineStr"/>
-      <c r="L32" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M32" s="5" t="inlineStr">
+      <c r="F32" s="9" t="inlineStr"/>
+      <c r="G32" s="9" t="inlineStr"/>
+      <c r="H32" s="9" t="inlineStr"/>
+      <c r="I32" s="9" t="inlineStr"/>
+      <c r="J32" s="9" t="inlineStr"/>
+      <c r="K32" s="9" t="inlineStr"/>
+      <c r="L32" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M32" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -2314,12 +2323,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O32" s="5" t="inlineStr">
+      <c r="O32" s="9" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="P32" s="5" t="inlineStr"/>
+      <c r="P32" s="9" t="inlineStr"/>
       <c r="Q32" s="7" t="inlineStr">
         <is>
           <t>https://maps.google.com/?cid=2127642918173484467&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -2327,43 +2336,43 @@
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="5" t="inlineStr"/>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="A33" s="9" t="inlineStr"/>
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>Sankofa Specialist Caterers</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>Food &amp; Hospitality</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D33" s="9" t="inlineStr">
         <is>
           <t>Gauteng</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E33" s="9" t="inlineStr">
         <is>
           <t>Menlyn</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F33" s="9" t="inlineStr">
         <is>
           <t>082 461 0321</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr"/>
-      <c r="H33" s="5" t="inlineStr"/>
-      <c r="I33" s="5" t="inlineStr"/>
-      <c r="J33" s="5" t="inlineStr"/>
-      <c r="K33" s="5" t="inlineStr"/>
-      <c r="L33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M33" s="5" t="inlineStr">
+      <c r="G33" s="9" t="inlineStr"/>
+      <c r="H33" s="9" t="inlineStr"/>
+      <c r="I33" s="9" t="inlineStr"/>
+      <c r="J33" s="9" t="inlineStr"/>
+      <c r="K33" s="9" t="inlineStr"/>
+      <c r="L33" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M33" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -2373,12 +2382,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O33" s="5" t="inlineStr">
+      <c r="O33" s="9" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="P33" s="5" t="inlineStr"/>
+      <c r="P33" s="9" t="inlineStr"/>
       <c r="Q33" s="7" t="inlineStr">
         <is>
           <t>5 stars | 4 reviews | Monday: 7:00 AM – 4:00 PM | Tuesday: 7:00 AM – 4:00 PM | Wednesday: 7:00 AM – 4:00 PM | https://maps.google.com/?cid=580253518917349460&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -2386,43 +2395,43 @@
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="5" t="inlineStr"/>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="A34" s="9" t="inlineStr"/>
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>MENLYN SELF CATERING</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>Food &amp; Hospitality</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr">
         <is>
           <t>Gauteng</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E34" s="9" t="inlineStr">
         <is>
           <t>Menlyn</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F34" s="9" t="inlineStr">
         <is>
           <t>076 288 8600</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr"/>
-      <c r="H34" s="5" t="inlineStr"/>
-      <c r="I34" s="5" t="inlineStr"/>
-      <c r="J34" s="5" t="inlineStr"/>
-      <c r="K34" s="5" t="inlineStr"/>
-      <c r="L34" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M34" s="5" t="inlineStr">
+      <c r="G34" s="9" t="inlineStr"/>
+      <c r="H34" s="9" t="inlineStr"/>
+      <c r="I34" s="9" t="inlineStr"/>
+      <c r="J34" s="9" t="inlineStr"/>
+      <c r="K34" s="9" t="inlineStr"/>
+      <c r="L34" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M34" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -2432,12 +2441,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O34" s="5" t="inlineStr">
+      <c r="O34" s="9" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="P34" s="5" t="inlineStr"/>
+      <c r="P34" s="9" t="inlineStr"/>
       <c r="Q34" s="7" t="inlineStr">
         <is>
           <t>Monday: 8:00 AM – 7:00 PM | Tuesday: 8:00 AM – 7:00 PM | Wednesday: 8:00 AM – 7:00 PM | https://maps.google.com/?cid=2465957039450054252&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -2445,43 +2454,43 @@
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="5" t="inlineStr"/>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="A35" s="9" t="inlineStr"/>
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>The Second Wife</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>Food &amp; Hospitality</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D35" s="9" t="inlineStr">
         <is>
           <t>KwaZulu-Natal</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E35" s="9" t="inlineStr">
         <is>
           <t>Chatsworth</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F35" s="9" t="inlineStr">
         <is>
           <t>061 133 1234</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr"/>
-      <c r="H35" s="5" t="inlineStr"/>
-      <c r="I35" s="5" t="inlineStr"/>
-      <c r="J35" s="5" t="inlineStr"/>
-      <c r="K35" s="5" t="inlineStr"/>
-      <c r="L35" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M35" s="5" t="inlineStr">
+      <c r="G35" s="9" t="inlineStr"/>
+      <c r="H35" s="9" t="inlineStr"/>
+      <c r="I35" s="9" t="inlineStr"/>
+      <c r="J35" s="9" t="inlineStr"/>
+      <c r="K35" s="9" t="inlineStr"/>
+      <c r="L35" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M35" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -2491,12 +2500,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O35" s="5" t="inlineStr">
+      <c r="O35" s="9" t="inlineStr">
         <is>
           <t>2026-04-04</t>
         </is>
       </c>
-      <c r="P35" s="5" t="inlineStr"/>
+      <c r="P35" s="9" t="inlineStr"/>
       <c r="Q35" s="7" t="inlineStr">
         <is>
           <t>3.5 stars | 253 reviews | Monday: 10:00 AM – 9:00 PM | Tuesday: 10:00 AM – 9:00 PM | Wednesday: 10:00 AM – 9:00 PM | https://maps.google.com/?cid=2346574056258469311&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -2504,43 +2513,43 @@
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="5" t="inlineStr"/>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="A36" s="9" t="inlineStr"/>
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>Copper Chimney</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>Food &amp; Hospitality</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D36" s="9" t="inlineStr">
         <is>
           <t>KwaZulu-Natal</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E36" s="9" t="inlineStr">
         <is>
           <t>Chatsworth</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F36" s="9" t="inlineStr">
         <is>
           <t>031 401 3812</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr"/>
-      <c r="H36" s="5" t="inlineStr"/>
-      <c r="I36" s="5" t="inlineStr"/>
-      <c r="J36" s="5" t="inlineStr"/>
-      <c r="K36" s="5" t="inlineStr"/>
-      <c r="L36" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M36" s="5" t="inlineStr">
+      <c r="G36" s="9" t="inlineStr"/>
+      <c r="H36" s="9" t="inlineStr"/>
+      <c r="I36" s="9" t="inlineStr"/>
+      <c r="J36" s="9" t="inlineStr"/>
+      <c r="K36" s="9" t="inlineStr"/>
+      <c r="L36" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M36" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -2550,12 +2559,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O36" s="5" t="inlineStr">
+      <c r="O36" s="9" t="inlineStr">
         <is>
           <t>2026-04-04</t>
         </is>
       </c>
-      <c r="P36" s="5" t="inlineStr"/>
+      <c r="P36" s="9" t="inlineStr"/>
       <c r="Q36" s="7" t="inlineStr">
         <is>
           <t>3.4 stars | 217 reviews | Monday: Open 24 hours | Tuesday: Open 24 hours | Wednesday: Open 24 hours | https://maps.google.com/?cid=2798449959599497030&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -2563,43 +2572,43 @@
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="5" t="inlineStr"/>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="A37" s="9" t="inlineStr"/>
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>Govinda's Restaurant &amp; Boutique</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
         <is>
           <t>Food &amp; Hospitality</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D37" s="9" t="inlineStr">
         <is>
           <t>KwaZulu-Natal</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E37" s="9" t="inlineStr">
         <is>
           <t>Chatsworth</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F37" s="9" t="inlineStr">
         <is>
           <t>031 403 3328</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr"/>
-      <c r="H37" s="5" t="inlineStr"/>
-      <c r="I37" s="5" t="inlineStr"/>
-      <c r="J37" s="5" t="inlineStr"/>
-      <c r="K37" s="5" t="inlineStr"/>
-      <c r="L37" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M37" s="5" t="inlineStr">
+      <c r="G37" s="9" t="inlineStr"/>
+      <c r="H37" s="9" t="inlineStr"/>
+      <c r="I37" s="9" t="inlineStr"/>
+      <c r="J37" s="9" t="inlineStr"/>
+      <c r="K37" s="9" t="inlineStr"/>
+      <c r="L37" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M37" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -2609,12 +2618,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O37" s="5" t="inlineStr">
+      <c r="O37" s="9" t="inlineStr">
         <is>
           <t>2026-04-04</t>
         </is>
       </c>
-      <c r="P37" s="5" t="inlineStr"/>
+      <c r="P37" s="9" t="inlineStr"/>
       <c r="Q37" s="7" t="inlineStr">
         <is>
           <t>4.7 stars | 55 reviews | Monday: 9:30 AM – 6:00 PM | Tuesday: 9:30 AM – 6:00 PM | Wednesday: 9:30 AM – 6:00 PM | https://maps.google.com/?cid=14320850139577209005&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -2622,39 +2631,39 @@
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="5" t="inlineStr"/>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="A38" s="9" t="inlineStr"/>
+      <c r="B38" s="9" t="inlineStr">
         <is>
           <t>Checotah Spur Steak Ranch (Halaal)</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>Food &amp; Hospitality</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D38" s="9" t="inlineStr">
         <is>
           <t>KwaZulu-Natal</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E38" s="9" t="inlineStr">
         <is>
           <t>Chatsworth</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr"/>
-      <c r="G38" s="5" t="inlineStr"/>
-      <c r="H38" s="5" t="inlineStr"/>
-      <c r="I38" s="5" t="inlineStr"/>
-      <c r="J38" s="5" t="inlineStr"/>
-      <c r="K38" s="5" t="inlineStr"/>
-      <c r="L38" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M38" s="5" t="inlineStr">
+      <c r="F38" s="9" t="inlineStr"/>
+      <c r="G38" s="9" t="inlineStr"/>
+      <c r="H38" s="9" t="inlineStr"/>
+      <c r="I38" s="9" t="inlineStr"/>
+      <c r="J38" s="9" t="inlineStr"/>
+      <c r="K38" s="9" t="inlineStr"/>
+      <c r="L38" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M38" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -2664,12 +2673,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O38" s="5" t="inlineStr">
+      <c r="O38" s="9" t="inlineStr">
         <is>
           <t>2026-04-04</t>
         </is>
       </c>
-      <c r="P38" s="5" t="inlineStr"/>
+      <c r="P38" s="9" t="inlineStr"/>
       <c r="Q38" s="7" t="inlineStr">
         <is>
           <t>4.1 stars | 1049 reviews | Monday: 8:00 AM – 9:00 PM | Tuesday: 8:00 AM – 9:00 PM | Wednesday: 8:00 AM – 9:00 PM | https://maps.google.com/?cid=5953807309119302951&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -2677,43 +2686,43 @@
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="5" t="inlineStr"/>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="A39" s="9" t="inlineStr"/>
+      <c r="B39" s="9" t="inlineStr">
         <is>
           <t>Cronos Moreleta Park Plumbers &amp; Electricians</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C39" s="9" t="inlineStr">
         <is>
           <t>Trades &amp; Home Services</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D39" s="9" t="inlineStr">
         <is>
           <t>Gauteng</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E39" s="9" t="inlineStr">
         <is>
           <t>Pretoria East</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F39" s="9" t="inlineStr">
         <is>
           <t>069 595 3715</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr"/>
-      <c r="H39" s="5" t="inlineStr"/>
-      <c r="I39" s="5" t="inlineStr"/>
-      <c r="J39" s="5" t="inlineStr"/>
-      <c r="K39" s="5" t="inlineStr"/>
-      <c r="L39" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M39" s="5" t="inlineStr">
+      <c r="G39" s="9" t="inlineStr"/>
+      <c r="H39" s="9" t="inlineStr"/>
+      <c r="I39" s="9" t="inlineStr"/>
+      <c r="J39" s="9" t="inlineStr"/>
+      <c r="K39" s="9" t="inlineStr"/>
+      <c r="L39" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M39" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -2723,12 +2732,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O39" s="5" t="inlineStr">
+      <c r="O39" s="9" t="inlineStr">
         <is>
           <t>2026-04-04</t>
         </is>
       </c>
-      <c r="P39" s="5" t="inlineStr"/>
+      <c r="P39" s="9" t="inlineStr"/>
       <c r="Q39" s="7" t="inlineStr">
         <is>
           <t>4.7 stars | 14 reviews | Monday: Open 24 hours | Tuesday: Open 24 hours | Wednesday: Open 24 hours | https://maps.google.com/?cid=3588421573338864152&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -2736,43 +2745,43 @@
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="5" t="inlineStr"/>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="A40" s="9" t="inlineStr"/>
+      <c r="B40" s="9" t="inlineStr">
         <is>
           <t>CR Plumbers &amp; Electricians-Garsfontein</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C40" s="9" t="inlineStr">
         <is>
           <t>Trades &amp; Home Services</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D40" s="9" t="inlineStr">
         <is>
           <t>Gauteng</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E40" s="9" t="inlineStr">
         <is>
           <t>Pretoria East</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="F40" s="9" t="inlineStr">
         <is>
           <t>084 684 5336</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr"/>
-      <c r="H40" s="5" t="inlineStr"/>
-      <c r="I40" s="5" t="inlineStr"/>
-      <c r="J40" s="5" t="inlineStr"/>
-      <c r="K40" s="5" t="inlineStr"/>
-      <c r="L40" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M40" s="5" t="inlineStr">
+      <c r="G40" s="9" t="inlineStr"/>
+      <c r="H40" s="9" t="inlineStr"/>
+      <c r="I40" s="9" t="inlineStr"/>
+      <c r="J40" s="9" t="inlineStr"/>
+      <c r="K40" s="9" t="inlineStr"/>
+      <c r="L40" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M40" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -2782,12 +2791,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O40" s="5" t="inlineStr">
+      <c r="O40" s="9" t="inlineStr">
         <is>
           <t>2026-04-04</t>
         </is>
       </c>
-      <c r="P40" s="5" t="inlineStr"/>
+      <c r="P40" s="9" t="inlineStr"/>
       <c r="Q40" s="7" t="inlineStr">
         <is>
           <t>4.6 stars | 44 reviews | Monday: Open 24 hours | Tuesday: Open 24 hours | Wednesday: Open 24 hours | https://maps.google.com/?cid=2899791334340290673&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -2795,43 +2804,43 @@
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="5" t="inlineStr"/>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="A41" s="9" t="inlineStr"/>
+      <c r="B41" s="9" t="inlineStr">
         <is>
           <t>LJs Lash&amp;Beauty Lounge</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C41" s="9" t="inlineStr">
         <is>
           <t>Beauty &amp; Wellness</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D41" s="9" t="inlineStr">
         <is>
           <t>Western Cape</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E41" s="9" t="inlineStr">
         <is>
           <t>Durbanville</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F41" s="9" t="inlineStr">
         <is>
           <t>060 675 2114</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr"/>
-      <c r="H41" s="5" t="inlineStr"/>
-      <c r="I41" s="5" t="inlineStr"/>
-      <c r="J41" s="5" t="inlineStr"/>
-      <c r="K41" s="5" t="inlineStr"/>
-      <c r="L41" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M41" s="5" t="inlineStr">
+      <c r="G41" s="9" t="inlineStr"/>
+      <c r="H41" s="9" t="inlineStr"/>
+      <c r="I41" s="9" t="inlineStr"/>
+      <c r="J41" s="9" t="inlineStr"/>
+      <c r="K41" s="9" t="inlineStr"/>
+      <c r="L41" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M41" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -2841,12 +2850,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O41" s="5" t="inlineStr">
+      <c r="O41" s="9" t="inlineStr">
         <is>
           <t>2026-04-04</t>
         </is>
       </c>
-      <c r="P41" s="5" t="inlineStr"/>
+      <c r="P41" s="9" t="inlineStr"/>
       <c r="Q41" s="7" t="inlineStr">
         <is>
           <t>4.7 stars | 11 reviews | Monday: 9:00 AM – 5:00 PM | Tuesday: 9:00 AM – 7:00 PM | Wednesday: 9:00 AM – 5:00 PM | https://maps.google.com/?cid=9576612907672604464&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -2854,39 +2863,39 @@
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="5" t="inlineStr"/>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="A42" s="9" t="inlineStr"/>
+      <c r="B42" s="9" t="inlineStr">
         <is>
           <t>Aesthetics By Bronwen</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C42" s="9" t="inlineStr">
         <is>
           <t>Beauty &amp; Wellness</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D42" s="9" t="inlineStr">
         <is>
           <t>Western Cape</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E42" s="9" t="inlineStr">
         <is>
           <t>Durbanville</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr"/>
-      <c r="G42" s="5" t="inlineStr"/>
-      <c r="H42" s="5" t="inlineStr"/>
-      <c r="I42" s="5" t="inlineStr"/>
-      <c r="J42" s="5" t="inlineStr"/>
-      <c r="K42" s="5" t="inlineStr"/>
-      <c r="L42" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M42" s="5" t="inlineStr">
+      <c r="F42" s="9" t="inlineStr"/>
+      <c r="G42" s="9" t="inlineStr"/>
+      <c r="H42" s="9" t="inlineStr"/>
+      <c r="I42" s="9" t="inlineStr"/>
+      <c r="J42" s="9" t="inlineStr"/>
+      <c r="K42" s="9" t="inlineStr"/>
+      <c r="L42" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M42" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -2896,12 +2905,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O42" s="5" t="inlineStr">
+      <c r="O42" s="9" t="inlineStr">
         <is>
           <t>2026-04-04</t>
         </is>
       </c>
-      <c r="P42" s="5" t="inlineStr"/>
+      <c r="P42" s="9" t="inlineStr"/>
       <c r="Q42" s="7" t="inlineStr">
         <is>
           <t>5 stars | 10 reviews | Monday: 9:30 AM – 6:00 PM | Tuesday: Closed | Wednesday: 9:30 AM – 5:00 PM | https://maps.google.com/?cid=17404010385463475815&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -2909,43 +2918,43 @@
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="5" t="inlineStr"/>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="A43" s="9" t="inlineStr"/>
+      <c r="B43" s="9" t="inlineStr">
         <is>
           <t>Domino's Pizza Halaal</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C43" s="9" t="inlineStr">
         <is>
           <t>Food &amp; Hospitality</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D43" s="9" t="inlineStr">
         <is>
           <t>KwaZulu-Natal</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E43" s="9" t="inlineStr">
         <is>
           <t>Berea</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F43" s="9" t="inlineStr">
         <is>
           <t>082 667 6578</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr"/>
-      <c r="H43" s="5" t="inlineStr"/>
-      <c r="I43" s="5" t="inlineStr"/>
-      <c r="J43" s="5" t="inlineStr"/>
-      <c r="K43" s="5" t="inlineStr"/>
-      <c r="L43" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M43" s="5" t="inlineStr">
+      <c r="G43" s="9" t="inlineStr"/>
+      <c r="H43" s="9" t="inlineStr"/>
+      <c r="I43" s="9" t="inlineStr"/>
+      <c r="J43" s="9" t="inlineStr"/>
+      <c r="K43" s="9" t="inlineStr"/>
+      <c r="L43" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M43" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -2955,12 +2964,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O43" s="5" t="inlineStr">
+      <c r="O43" s="9" t="inlineStr">
         <is>
           <t>2026-04-05</t>
         </is>
       </c>
-      <c r="P43" s="5" t="inlineStr"/>
+      <c r="P43" s="9" t="inlineStr"/>
       <c r="Q43" s="7" t="inlineStr">
         <is>
           <t>4.3 stars | 9 reviews | Monday: 10:30 AM – 9:00 PM | Tuesday: 10:30 AM – 9:00 PM | Wednesday: 10:30 AM – 9:00 PM | https://maps.google.com/?cid=9753225131831671488&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -2968,43 +2977,43 @@
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="5" t="inlineStr"/>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="A44" s="9" t="inlineStr"/>
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>Maths Medic</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C44" s="9" t="inlineStr">
         <is>
           <t>Professional Services</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D44" s="9" t="inlineStr">
         <is>
           <t>Western Cape</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E44" s="9" t="inlineStr">
         <is>
           <t>Table View</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F44" s="9" t="inlineStr">
         <is>
           <t>083 448 8090</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr"/>
-      <c r="H44" s="5" t="inlineStr"/>
-      <c r="I44" s="5" t="inlineStr"/>
-      <c r="J44" s="5" t="inlineStr"/>
-      <c r="K44" s="5" t="inlineStr"/>
-      <c r="L44" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M44" s="5" t="inlineStr">
+      <c r="G44" s="9" t="inlineStr"/>
+      <c r="H44" s="9" t="inlineStr"/>
+      <c r="I44" s="9" t="inlineStr"/>
+      <c r="J44" s="9" t="inlineStr"/>
+      <c r="K44" s="9" t="inlineStr"/>
+      <c r="L44" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M44" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -3014,12 +3023,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O44" s="5" t="inlineStr">
+      <c r="O44" s="9" t="inlineStr">
         <is>
           <t>2026-04-05</t>
         </is>
       </c>
-      <c r="P44" s="5" t="inlineStr"/>
+      <c r="P44" s="9" t="inlineStr"/>
       <c r="Q44" s="7" t="inlineStr">
         <is>
           <t>4.8 stars | 36 reviews | Monday: 8:30 AM – 9:00 PM | Tuesday: 8:30 AM – 9:00 PM | Wednesday: 8:30 AM – 9:00 PM | https://maps.google.com/?cid=6923866599004797613&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -3027,43 +3036,43 @@
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="5" t="inlineStr"/>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="A45" s="9" t="inlineStr"/>
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>Sandi's Home Based After care and homework assistance.</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C45" s="9" t="inlineStr">
         <is>
           <t>Professional Services</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D45" s="9" t="inlineStr">
         <is>
           <t>Western Cape</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E45" s="9" t="inlineStr">
         <is>
           <t>Table View</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F45" s="9" t="inlineStr">
         <is>
           <t>076 148 8309</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr"/>
-      <c r="H45" s="5" t="inlineStr"/>
-      <c r="I45" s="5" t="inlineStr"/>
-      <c r="J45" s="5" t="inlineStr"/>
-      <c r="K45" s="5" t="inlineStr"/>
-      <c r="L45" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M45" s="5" t="inlineStr">
+      <c r="G45" s="9" t="inlineStr"/>
+      <c r="H45" s="9" t="inlineStr"/>
+      <c r="I45" s="9" t="inlineStr"/>
+      <c r="J45" s="9" t="inlineStr"/>
+      <c r="K45" s="9" t="inlineStr"/>
+      <c r="L45" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M45" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -3073,12 +3082,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O45" s="5" t="inlineStr">
+      <c r="O45" s="9" t="inlineStr">
         <is>
           <t>2026-04-05</t>
         </is>
       </c>
-      <c r="P45" s="5" t="inlineStr"/>
+      <c r="P45" s="9" t="inlineStr"/>
       <c r="Q45" s="7" t="inlineStr">
         <is>
           <t>5 stars | 11 reviews | Monday: 1:30 – 5:15 PM | Tuesday: 1:30 – 5:15 PM | Wednesday: 1:30 – 5:15 PM | https://maps.google.com/?cid=8796849888630976869&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -3086,43 +3095,43 @@
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="5" t="inlineStr"/>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="A46" s="9" t="inlineStr"/>
+      <c r="B46" s="9" t="inlineStr">
         <is>
           <t>Dynamic Academy Tutoring Centre</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C46" s="9" t="inlineStr">
         <is>
           <t>Professional Services</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D46" s="9" t="inlineStr">
         <is>
           <t>Western Cape</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E46" s="9" t="inlineStr">
         <is>
           <t>Table View</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="F46" s="9" t="inlineStr">
         <is>
           <t>079 761 0789</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr"/>
-      <c r="H46" s="5" t="inlineStr"/>
-      <c r="I46" s="5" t="inlineStr"/>
-      <c r="J46" s="5" t="inlineStr"/>
-      <c r="K46" s="5" t="inlineStr"/>
-      <c r="L46" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M46" s="5" t="inlineStr">
+      <c r="G46" s="9" t="inlineStr"/>
+      <c r="H46" s="9" t="inlineStr"/>
+      <c r="I46" s="9" t="inlineStr"/>
+      <c r="J46" s="9" t="inlineStr"/>
+      <c r="K46" s="9" t="inlineStr"/>
+      <c r="L46" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M46" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -3132,12 +3141,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O46" s="5" t="inlineStr">
+      <c r="O46" s="9" t="inlineStr">
         <is>
           <t>2026-04-05</t>
         </is>
       </c>
-      <c r="P46" s="5" t="inlineStr"/>
+      <c r="P46" s="9" t="inlineStr"/>
       <c r="Q46" s="7" t="inlineStr">
         <is>
           <t>2.8 stars | 6 reviews | Monday: 8:00 AM – 2:00 PM | Tuesday: 8:00 AM – 2:00 PM | Wednesday: 8:00 AM – 2:00 PM | https://maps.google.com/?cid=413935781571611112&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -3145,43 +3154,43 @@
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="5" t="inlineStr"/>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="A47" s="9" t="inlineStr"/>
+      <c r="B47" s="9" t="inlineStr">
         <is>
           <t>Math Science Boffin</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C47" s="9" t="inlineStr">
         <is>
           <t>Professional Services</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D47" s="9" t="inlineStr">
         <is>
           <t>Western Cape</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E47" s="9" t="inlineStr">
         <is>
           <t>Table View</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="F47" s="9" t="inlineStr">
         <is>
           <t>061 488 6697</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr"/>
-      <c r="H47" s="5" t="inlineStr"/>
-      <c r="I47" s="5" t="inlineStr"/>
-      <c r="J47" s="5" t="inlineStr"/>
-      <c r="K47" s="5" t="inlineStr"/>
-      <c r="L47" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M47" s="5" t="inlineStr">
+      <c r="G47" s="9" t="inlineStr"/>
+      <c r="H47" s="9" t="inlineStr"/>
+      <c r="I47" s="9" t="inlineStr"/>
+      <c r="J47" s="9" t="inlineStr"/>
+      <c r="K47" s="9" t="inlineStr"/>
+      <c r="L47" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M47" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -3191,12 +3200,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O47" s="5" t="inlineStr">
+      <c r="O47" s="9" t="inlineStr">
         <is>
           <t>2026-04-05</t>
         </is>
       </c>
-      <c r="P47" s="5" t="inlineStr"/>
+      <c r="P47" s="9" t="inlineStr"/>
       <c r="Q47" s="7" t="inlineStr">
         <is>
           <t>Monday: 8:00 AM – 5:00 PM | Tuesday: 8:00 AM – 5:00 PM | Wednesday: 8:00 AM – 5:00 PM | https://maps.google.com/?cid=9959668364455373267&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -3204,43 +3213,43 @@
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="5" t="inlineStr"/>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="A48" s="9" t="inlineStr"/>
+      <c r="B48" s="9" t="inlineStr">
         <is>
           <t>Master Quest Tutors</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C48" s="9" t="inlineStr">
         <is>
           <t>Professional Services</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D48" s="9" t="inlineStr">
         <is>
           <t>Western Cape</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E48" s="9" t="inlineStr">
         <is>
           <t>Table View</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="F48" s="9" t="inlineStr">
         <is>
           <t>061 403 3144</t>
         </is>
       </c>
-      <c r="G48" s="5" t="inlineStr"/>
-      <c r="H48" s="5" t="inlineStr"/>
-      <c r="I48" s="5" t="inlineStr"/>
-      <c r="J48" s="5" t="inlineStr"/>
-      <c r="K48" s="5" t="inlineStr"/>
-      <c r="L48" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M48" s="5" t="inlineStr">
+      <c r="G48" s="9" t="inlineStr"/>
+      <c r="H48" s="9" t="inlineStr"/>
+      <c r="I48" s="9" t="inlineStr"/>
+      <c r="J48" s="9" t="inlineStr"/>
+      <c r="K48" s="9" t="inlineStr"/>
+      <c r="L48" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M48" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -3250,12 +3259,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O48" s="5" t="inlineStr">
+      <c r="O48" s="9" t="inlineStr">
         <is>
           <t>2026-04-05</t>
         </is>
       </c>
-      <c r="P48" s="5" t="inlineStr"/>
+      <c r="P48" s="9" t="inlineStr"/>
       <c r="Q48" s="7" t="inlineStr">
         <is>
           <t>Monday: 9:00 AM – 5:00 PM | Tuesday: 9:00 AM – 5:00 PM | Wednesday: 9:00 AM – 5:00 PM | https://maps.google.com/?cid=3801822804813934822&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -3263,43 +3272,43 @@
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="5" t="inlineStr"/>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="A49" s="9" t="inlineStr"/>
+      <c r="B49" s="9" t="inlineStr">
         <is>
           <t>TJVZ - 1519 Locksmiths and General Maintenance Services</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C49" s="9" t="inlineStr">
         <is>
           <t>Trades &amp; Home Services</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D49" s="9" t="inlineStr">
         <is>
           <t>Western Cape</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E49" s="9" t="inlineStr">
         <is>
           <t>Durbanville</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F49" s="9" t="inlineStr">
         <is>
           <t>071 483 7953</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr"/>
-      <c r="H49" s="5" t="inlineStr"/>
-      <c r="I49" s="5" t="inlineStr"/>
-      <c r="J49" s="5" t="inlineStr"/>
-      <c r="K49" s="5" t="inlineStr"/>
-      <c r="L49" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M49" s="5" t="inlineStr">
+      <c r="G49" s="9" t="inlineStr"/>
+      <c r="H49" s="9" t="inlineStr"/>
+      <c r="I49" s="9" t="inlineStr"/>
+      <c r="J49" s="9" t="inlineStr"/>
+      <c r="K49" s="9" t="inlineStr"/>
+      <c r="L49" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M49" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -3309,12 +3318,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O49" s="5" t="inlineStr">
+      <c r="O49" s="9" t="inlineStr">
         <is>
           <t>2026-04-05</t>
         </is>
       </c>
-      <c r="P49" s="5" t="inlineStr"/>
+      <c r="P49" s="9" t="inlineStr"/>
       <c r="Q49" s="7" t="inlineStr">
         <is>
           <t>5 stars | 6 reviews | Monday: Open 24 hours | Tuesday: Open 24 hours | Wednesday: Open 24 hours | https://maps.google.com/?cid=12468206334505191803&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -3322,43 +3331,43 @@
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="5" t="inlineStr"/>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="A50" s="9" t="inlineStr"/>
+      <c r="B50" s="9" t="inlineStr">
         <is>
           <t>Prag Shoe Repairs And Locksmiths</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C50" s="9" t="inlineStr">
         <is>
           <t>Trades &amp; Home Services</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D50" s="9" t="inlineStr">
         <is>
           <t>Western Cape</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E50" s="9" t="inlineStr">
         <is>
           <t>Durbanville</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="F50" s="9" t="inlineStr">
         <is>
           <t>079 285 7645</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr"/>
-      <c r="H50" s="5" t="inlineStr"/>
-      <c r="I50" s="5" t="inlineStr"/>
-      <c r="J50" s="5" t="inlineStr"/>
-      <c r="K50" s="5" t="inlineStr"/>
-      <c r="L50" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M50" s="5" t="inlineStr">
+      <c r="G50" s="9" t="inlineStr"/>
+      <c r="H50" s="9" t="inlineStr"/>
+      <c r="I50" s="9" t="inlineStr"/>
+      <c r="J50" s="9" t="inlineStr"/>
+      <c r="K50" s="9" t="inlineStr"/>
+      <c r="L50" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M50" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -3368,12 +3377,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O50" s="5" t="inlineStr">
+      <c r="O50" s="9" t="inlineStr">
         <is>
           <t>2026-04-05</t>
         </is>
       </c>
-      <c r="P50" s="5" t="inlineStr"/>
+      <c r="P50" s="9" t="inlineStr"/>
       <c r="Q50" s="7" t="inlineStr">
         <is>
           <t>4.6 stars | 35 reviews | Monday: 8:00 AM – 5:00 PM | Tuesday: 8:00 AM – 5:00 PM | Wednesday: 8:00 AM – 5:00 PM | https://maps.google.com/?cid=10981293976912651312&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -3381,43 +3390,43 @@
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="5" t="inlineStr"/>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="A51" s="9" t="inlineStr"/>
+      <c r="B51" s="9" t="inlineStr">
         <is>
           <t>Hatfield City Plumbers &amp; Electricians</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C51" s="9" t="inlineStr">
         <is>
           <t>Trades &amp; Home Services</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D51" s="9" t="inlineStr">
         <is>
           <t>Gauteng</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E51" s="9" t="inlineStr">
         <is>
           <t>Hatfield</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="F51" s="9" t="inlineStr">
         <is>
           <t>075 387 9410</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr"/>
-      <c r="H51" s="5" t="inlineStr"/>
-      <c r="I51" s="5" t="inlineStr"/>
-      <c r="J51" s="5" t="inlineStr"/>
-      <c r="K51" s="5" t="inlineStr"/>
-      <c r="L51" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M51" s="5" t="inlineStr">
+      <c r="G51" s="9" t="inlineStr"/>
+      <c r="H51" s="9" t="inlineStr"/>
+      <c r="I51" s="9" t="inlineStr"/>
+      <c r="J51" s="9" t="inlineStr"/>
+      <c r="K51" s="9" t="inlineStr"/>
+      <c r="L51" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M51" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -3427,12 +3436,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O51" s="5" t="inlineStr">
+      <c r="O51" s="9" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="P51" s="5" t="inlineStr"/>
+      <c r="P51" s="9" t="inlineStr"/>
       <c r="Q51" s="7" t="inlineStr">
         <is>
           <t>5 stars | 9 reviews | Monday: Open 24 hours | Tuesday: Open 24 hours | Wednesday: Open 24 hours | https://maps.google.com/?cid=16535670141058677428&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -3440,43 +3449,43 @@
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="5" t="inlineStr"/>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="A52" s="9" t="inlineStr"/>
+      <c r="B52" s="9" t="inlineStr">
         <is>
           <t>N.U plumbers &amp; Electricians-Lynnwood</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C52" s="9" t="inlineStr">
         <is>
           <t>Trades &amp; Home Services</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D52" s="9" t="inlineStr">
         <is>
           <t>Gauteng</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E52" s="9" t="inlineStr">
         <is>
           <t>Hatfield</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="F52" s="9" t="inlineStr">
         <is>
           <t>060 378 9778</t>
         </is>
       </c>
-      <c r="G52" s="5" t="inlineStr"/>
-      <c r="H52" s="5" t="inlineStr"/>
-      <c r="I52" s="5" t="inlineStr"/>
-      <c r="J52" s="5" t="inlineStr"/>
-      <c r="K52" s="5" t="inlineStr"/>
-      <c r="L52" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M52" s="5" t="inlineStr">
+      <c r="G52" s="9" t="inlineStr"/>
+      <c r="H52" s="9" t="inlineStr"/>
+      <c r="I52" s="9" t="inlineStr"/>
+      <c r="J52" s="9" t="inlineStr"/>
+      <c r="K52" s="9" t="inlineStr"/>
+      <c r="L52" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M52" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -3486,12 +3495,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O52" s="5" t="inlineStr">
+      <c r="O52" s="9" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="P52" s="5" t="inlineStr"/>
+      <c r="P52" s="9" t="inlineStr"/>
       <c r="Q52" s="7" t="inlineStr">
         <is>
           <t>4.9 stars | 39 reviews | Monday: Open 24 hours | Tuesday: Open 24 hours | Wednesday: Open 24 hours | https://maps.google.com/?cid=6935163348323535180&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -3499,43 +3508,43 @@
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="5" t="inlineStr"/>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="A53" s="9" t="inlineStr"/>
+      <c r="B53" s="9" t="inlineStr">
         <is>
           <t>Rats plumbing</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C53" s="9" t="inlineStr">
         <is>
           <t>Trades &amp; Home Services</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D53" s="9" t="inlineStr">
         <is>
           <t>Gauteng</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr">
+      <c r="E53" s="9" t="inlineStr">
         <is>
           <t>Hatfield</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="F53" s="9" t="inlineStr">
         <is>
           <t>064 709 7289</t>
         </is>
       </c>
-      <c r="G53" s="5" t="inlineStr"/>
-      <c r="H53" s="5" t="inlineStr"/>
-      <c r="I53" s="5" t="inlineStr"/>
-      <c r="J53" s="5" t="inlineStr"/>
-      <c r="K53" s="5" t="inlineStr"/>
-      <c r="L53" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M53" s="5" t="inlineStr">
+      <c r="G53" s="9" t="inlineStr"/>
+      <c r="H53" s="9" t="inlineStr"/>
+      <c r="I53" s="9" t="inlineStr"/>
+      <c r="J53" s="9" t="inlineStr"/>
+      <c r="K53" s="9" t="inlineStr"/>
+      <c r="L53" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M53" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -3545,12 +3554,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O53" s="5" t="inlineStr">
+      <c r="O53" s="9" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="P53" s="5" t="inlineStr"/>
+      <c r="P53" s="9" t="inlineStr"/>
       <c r="Q53" s="7" t="inlineStr">
         <is>
           <t>https://maps.google.com/?cid=1535336020316692418&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -3558,43 +3567,43 @@
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="5" t="inlineStr"/>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="A54" s="9" t="inlineStr"/>
+      <c r="B54" s="9" t="inlineStr">
         <is>
           <t>Ehlers Bernd Tiling &amp; Modernising CC</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C54" s="9" t="inlineStr">
         <is>
           <t>Trades &amp; Home Services</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D54" s="9" t="inlineStr">
         <is>
           <t>Gauteng</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr">
+      <c r="E54" s="9" t="inlineStr">
         <is>
           <t>Bryanston</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="F54" s="9" t="inlineStr">
         <is>
           <t>011 614 6035</t>
         </is>
       </c>
-      <c r="G54" s="5" t="inlineStr"/>
-      <c r="H54" s="5" t="inlineStr"/>
-      <c r="I54" s="5" t="inlineStr"/>
-      <c r="J54" s="5" t="inlineStr"/>
-      <c r="K54" s="5" t="inlineStr"/>
-      <c r="L54" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M54" s="5" t="inlineStr">
+      <c r="G54" s="9" t="inlineStr"/>
+      <c r="H54" s="9" t="inlineStr"/>
+      <c r="I54" s="9" t="inlineStr"/>
+      <c r="J54" s="9" t="inlineStr"/>
+      <c r="K54" s="9" t="inlineStr"/>
+      <c r="L54" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M54" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -3604,12 +3613,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O54" s="5" t="inlineStr">
+      <c r="O54" s="9" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="P54" s="5" t="inlineStr"/>
+      <c r="P54" s="9" t="inlineStr"/>
       <c r="Q54" s="7" t="inlineStr">
         <is>
           <t>5 stars | 1 reviews | Monday: 8:00 AM – 5:00 PM | Tuesday: 8:00 AM – 5:00 PM | Wednesday: 8:00 AM – 5:00 PM | https://maps.google.com/?cid=12202758347105124936&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -3617,43 +3626,43 @@
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="5" t="inlineStr"/>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="A55" s="9" t="inlineStr"/>
+      <c r="B55" s="9" t="inlineStr">
         <is>
           <t>Building &amp; Renovators Project, Plumber, Electrician, tiler, home renovations</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C55" s="9" t="inlineStr">
         <is>
           <t>Trades &amp; Home Services</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D55" s="9" t="inlineStr">
         <is>
           <t>Gauteng</t>
         </is>
       </c>
-      <c r="E55" s="5" t="inlineStr">
+      <c r="E55" s="9" t="inlineStr">
         <is>
           <t>Bryanston</t>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="F55" s="9" t="inlineStr">
         <is>
           <t>083 645 4329</t>
         </is>
       </c>
-      <c r="G55" s="5" t="inlineStr"/>
-      <c r="H55" s="5" t="inlineStr"/>
-      <c r="I55" s="5" t="inlineStr"/>
-      <c r="J55" s="5" t="inlineStr"/>
-      <c r="K55" s="5" t="inlineStr"/>
-      <c r="L55" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M55" s="5" t="inlineStr">
+      <c r="G55" s="9" t="inlineStr"/>
+      <c r="H55" s="9" t="inlineStr"/>
+      <c r="I55" s="9" t="inlineStr"/>
+      <c r="J55" s="9" t="inlineStr"/>
+      <c r="K55" s="9" t="inlineStr"/>
+      <c r="L55" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M55" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -3663,12 +3672,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O55" s="5" t="inlineStr">
+      <c r="O55" s="9" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="P55" s="5" t="inlineStr"/>
+      <c r="P55" s="9" t="inlineStr"/>
       <c r="Q55" s="7" t="inlineStr">
         <is>
           <t>5 stars | 1 reviews | Monday: 7:30 AM – 5:00 PM | Tuesday: 7:00 AM – 5:00 PM | Wednesday: 7:00 AM – 5:00 PM | https://maps.google.com/?cid=9731750060488759204&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -3676,43 +3685,43 @@
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="5" t="inlineStr"/>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="A56" s="9" t="inlineStr"/>
+      <c r="B56" s="9" t="inlineStr">
         <is>
           <t>Tiling Services</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C56" s="9" t="inlineStr">
         <is>
           <t>Trades &amp; Home Services</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D56" s="9" t="inlineStr">
         <is>
           <t>Gauteng</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
+      <c r="E56" s="9" t="inlineStr">
         <is>
           <t>Bryanston</t>
         </is>
       </c>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="F56" s="9" t="inlineStr">
         <is>
           <t>072 073 9856</t>
         </is>
       </c>
-      <c r="G56" s="5" t="inlineStr"/>
-      <c r="H56" s="5" t="inlineStr"/>
-      <c r="I56" s="5" t="inlineStr"/>
-      <c r="J56" s="5" t="inlineStr"/>
-      <c r="K56" s="5" t="inlineStr"/>
-      <c r="L56" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M56" s="5" t="inlineStr">
+      <c r="G56" s="9" t="inlineStr"/>
+      <c r="H56" s="9" t="inlineStr"/>
+      <c r="I56" s="9" t="inlineStr"/>
+      <c r="J56" s="9" t="inlineStr"/>
+      <c r="K56" s="9" t="inlineStr"/>
+      <c r="L56" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M56" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -3722,12 +3731,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O56" s="5" t="inlineStr">
+      <c r="O56" s="9" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="P56" s="5" t="inlineStr"/>
+      <c r="P56" s="9" t="inlineStr"/>
       <c r="Q56" s="7" t="inlineStr">
         <is>
           <t>5 stars | 1 reviews | https://maps.google.com/?cid=16091882776789115807&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -3735,43 +3744,43 @@
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="5" t="inlineStr"/>
-      <c r="B57" s="5" t="inlineStr">
+      <c r="A57" s="9" t="inlineStr"/>
+      <c r="B57" s="9" t="inlineStr">
         <is>
           <t>Zekuwe Tiling</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C57" s="9" t="inlineStr">
         <is>
           <t>Trades &amp; Home Services</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="D57" s="9" t="inlineStr">
         <is>
           <t>Gauteng</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr">
+      <c r="E57" s="9" t="inlineStr">
         <is>
           <t>Bryanston</t>
         </is>
       </c>
-      <c r="F57" s="5" t="inlineStr">
+      <c r="F57" s="9" t="inlineStr">
         <is>
           <t>010 140 6510</t>
         </is>
       </c>
-      <c r="G57" s="5" t="inlineStr"/>
-      <c r="H57" s="5" t="inlineStr"/>
-      <c r="I57" s="5" t="inlineStr"/>
-      <c r="J57" s="5" t="inlineStr"/>
-      <c r="K57" s="5" t="inlineStr"/>
-      <c r="L57" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M57" s="5" t="inlineStr">
+      <c r="G57" s="9" t="inlineStr"/>
+      <c r="H57" s="9" t="inlineStr"/>
+      <c r="I57" s="9" t="inlineStr"/>
+      <c r="J57" s="9" t="inlineStr"/>
+      <c r="K57" s="9" t="inlineStr"/>
+      <c r="L57" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M57" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -3781,12 +3790,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O57" s="5" t="inlineStr">
+      <c r="O57" s="9" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="P57" s="5" t="inlineStr"/>
+      <c r="P57" s="9" t="inlineStr"/>
       <c r="Q57" s="7" t="inlineStr">
         <is>
           <t>https://maps.google.com/?cid=17154198375586397953&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -3794,43 +3803,43 @@
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="5" t="inlineStr"/>
-      <c r="B58" s="5" t="inlineStr">
+      <c r="A58" s="9" t="inlineStr"/>
+      <c r="B58" s="9" t="inlineStr">
         <is>
           <t>Werner’s Vleismark</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C58" s="9" t="inlineStr">
         <is>
           <t>Food &amp; Hospitality</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D58" s="9" t="inlineStr">
         <is>
           <t>Western Cape</t>
         </is>
       </c>
-      <c r="E58" s="5" t="inlineStr">
+      <c r="E58" s="9" t="inlineStr">
         <is>
           <t>Strand</t>
         </is>
       </c>
-      <c r="F58" s="5" t="inlineStr">
+      <c r="F58" s="9" t="inlineStr">
         <is>
           <t>021 853 6605</t>
         </is>
       </c>
-      <c r="G58" s="5" t="inlineStr"/>
-      <c r="H58" s="5" t="inlineStr"/>
-      <c r="I58" s="5" t="inlineStr"/>
-      <c r="J58" s="5" t="inlineStr"/>
-      <c r="K58" s="5" t="inlineStr"/>
-      <c r="L58" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M58" s="5" t="inlineStr">
+      <c r="G58" s="9" t="inlineStr"/>
+      <c r="H58" s="9" t="inlineStr"/>
+      <c r="I58" s="9" t="inlineStr"/>
+      <c r="J58" s="9" t="inlineStr"/>
+      <c r="K58" s="9" t="inlineStr"/>
+      <c r="L58" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M58" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -3840,12 +3849,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O58" s="5" t="inlineStr">
+      <c r="O58" s="9" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="P58" s="5" t="inlineStr"/>
+      <c r="P58" s="9" t="inlineStr"/>
       <c r="Q58" s="7" t="inlineStr">
         <is>
           <t>4.6 stars | 639 reviews | Monday: 8:00 AM – 5:30 PM | Tuesday: 8:00 AM – 5:30 PM | Wednesday: 8:00 AM – 5:30 PM | https://maps.google.com/?cid=14139406209463898456&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -3853,43 +3862,43 @@
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="5" t="inlineStr"/>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="A59" s="9" t="inlineStr"/>
+      <c r="B59" s="9" t="inlineStr">
         <is>
           <t>The Butcher's Market (TBM)</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C59" s="9" t="inlineStr">
         <is>
           <t>Food &amp; Hospitality</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D59" s="9" t="inlineStr">
         <is>
           <t>Western Cape</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr">
+      <c r="E59" s="9" t="inlineStr">
         <is>
           <t>Strand</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr">
+      <c r="F59" s="9" t="inlineStr">
         <is>
           <t>021 565 0729</t>
         </is>
       </c>
-      <c r="G59" s="5" t="inlineStr"/>
-      <c r="H59" s="5" t="inlineStr"/>
-      <c r="I59" s="5" t="inlineStr"/>
-      <c r="J59" s="5" t="inlineStr"/>
-      <c r="K59" s="5" t="inlineStr"/>
-      <c r="L59" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M59" s="5" t="inlineStr">
+      <c r="G59" s="9" t="inlineStr"/>
+      <c r="H59" s="9" t="inlineStr"/>
+      <c r="I59" s="9" t="inlineStr"/>
+      <c r="J59" s="9" t="inlineStr"/>
+      <c r="K59" s="9" t="inlineStr"/>
+      <c r="L59" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M59" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -3899,12 +3908,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O59" s="5" t="inlineStr">
+      <c r="O59" s="9" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="P59" s="5" t="inlineStr"/>
+      <c r="P59" s="9" t="inlineStr"/>
       <c r="Q59" s="7" t="inlineStr">
         <is>
           <t>4.3 stars | 28 reviews | Monday: 8:30 AM – 5:30 PM | Tuesday: 8:30 AM – 5:30 PM | Wednesday: 8:30 AM – 5:30 PM | https://maps.google.com/?cid=15066010833509353965&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -3912,43 +3921,43 @@
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="5" t="inlineStr"/>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="A60" s="9" t="inlineStr"/>
+      <c r="B60" s="9" t="inlineStr">
         <is>
           <t>W P Steyn Group - Vleis Groothandelaars Pty Ltd</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="C60" s="9" t="inlineStr">
         <is>
           <t>Food &amp; Hospitality</t>
         </is>
       </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="D60" s="9" t="inlineStr">
         <is>
           <t>Western Cape</t>
         </is>
       </c>
-      <c r="E60" s="5" t="inlineStr">
+      <c r="E60" s="9" t="inlineStr">
         <is>
           <t>Strand</t>
         </is>
       </c>
-      <c r="F60" s="5" t="inlineStr">
+      <c r="F60" s="9" t="inlineStr">
         <is>
           <t>021 853 6605</t>
         </is>
       </c>
-      <c r="G60" s="5" t="inlineStr"/>
-      <c r="H60" s="5" t="inlineStr"/>
-      <c r="I60" s="5" t="inlineStr"/>
-      <c r="J60" s="5" t="inlineStr"/>
-      <c r="K60" s="5" t="inlineStr"/>
-      <c r="L60" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M60" s="5" t="inlineStr">
+      <c r="G60" s="9" t="inlineStr"/>
+      <c r="H60" s="9" t="inlineStr"/>
+      <c r="I60" s="9" t="inlineStr"/>
+      <c r="J60" s="9" t="inlineStr"/>
+      <c r="K60" s="9" t="inlineStr"/>
+      <c r="L60" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M60" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -3958,12 +3967,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O60" s="5" t="inlineStr">
+      <c r="O60" s="9" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="P60" s="5" t="inlineStr"/>
+      <c r="P60" s="9" t="inlineStr"/>
       <c r="Q60" s="7" t="inlineStr">
         <is>
           <t>4.8 stars | 57 reviews | Monday: 7:00 AM – 4:00 PM | Tuesday: 7:00 AM – 4:00 PM | Wednesday: 7:00 AM – 4:00 PM | https://maps.google.com/?cid=16140257758762724582&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -3971,43 +3980,43 @@
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="5" t="inlineStr"/>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="A61" s="9" t="inlineStr"/>
+      <c r="B61" s="9" t="inlineStr">
         <is>
           <t>Roots Butchery Somerset Crossing</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C61" s="9" t="inlineStr">
         <is>
           <t>Food &amp; Hospitality</t>
         </is>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D61" s="9" t="inlineStr">
         <is>
           <t>Western Cape</t>
         </is>
       </c>
-      <c r="E61" s="5" t="inlineStr">
+      <c r="E61" s="9" t="inlineStr">
         <is>
           <t>Strand</t>
         </is>
       </c>
-      <c r="F61" s="5" t="inlineStr">
+      <c r="F61" s="9" t="inlineStr">
         <is>
           <t>022 007 0173</t>
         </is>
       </c>
-      <c r="G61" s="5" t="inlineStr"/>
-      <c r="H61" s="5" t="inlineStr"/>
-      <c r="I61" s="5" t="inlineStr"/>
-      <c r="J61" s="5" t="inlineStr"/>
-      <c r="K61" s="5" t="inlineStr"/>
-      <c r="L61" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M61" s="5" t="inlineStr">
+      <c r="G61" s="9" t="inlineStr"/>
+      <c r="H61" s="9" t="inlineStr"/>
+      <c r="I61" s="9" t="inlineStr"/>
+      <c r="J61" s="9" t="inlineStr"/>
+      <c r="K61" s="9" t="inlineStr"/>
+      <c r="L61" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M61" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -4017,12 +4026,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O61" s="5" t="inlineStr">
+      <c r="O61" s="9" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="P61" s="5" t="inlineStr"/>
+      <c r="P61" s="9" t="inlineStr"/>
       <c r="Q61" s="7" t="inlineStr">
         <is>
           <t>4.4 stars | 89 reviews | Monday: 9:00 AM – 7:00 PM | Tuesday: 9:00 AM – 7:00 PM | Wednesday: 9:00 AM – 7:00 PM | https://maps.google.com/?cid=3492656207435798340&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -4030,39 +4039,39 @@
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="5" t="inlineStr"/>
-      <c r="B62" s="5" t="inlineStr">
+      <c r="A62" s="9" t="inlineStr"/>
+      <c r="B62" s="9" t="inlineStr">
         <is>
           <t>Plaza Butchery</t>
         </is>
       </c>
-      <c r="C62" s="5" t="inlineStr">
+      <c r="C62" s="9" t="inlineStr">
         <is>
           <t>Food &amp; Hospitality</t>
         </is>
       </c>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="D62" s="9" t="inlineStr">
         <is>
           <t>Western Cape</t>
         </is>
       </c>
-      <c r="E62" s="5" t="inlineStr">
+      <c r="E62" s="9" t="inlineStr">
         <is>
           <t>Strand</t>
         </is>
       </c>
-      <c r="F62" s="5" t="inlineStr"/>
-      <c r="G62" s="5" t="inlineStr"/>
-      <c r="H62" s="5" t="inlineStr"/>
-      <c r="I62" s="5" t="inlineStr"/>
-      <c r="J62" s="5" t="inlineStr"/>
-      <c r="K62" s="5" t="inlineStr"/>
-      <c r="L62" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M62" s="5" t="inlineStr">
+      <c r="F62" s="9" t="inlineStr"/>
+      <c r="G62" s="9" t="inlineStr"/>
+      <c r="H62" s="9" t="inlineStr"/>
+      <c r="I62" s="9" t="inlineStr"/>
+      <c r="J62" s="9" t="inlineStr"/>
+      <c r="K62" s="9" t="inlineStr"/>
+      <c r="L62" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M62" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -4072,12 +4081,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O62" s="5" t="inlineStr">
+      <c r="O62" s="9" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="P62" s="5" t="inlineStr"/>
+      <c r="P62" s="9" t="inlineStr"/>
       <c r="Q62" s="7" t="inlineStr">
         <is>
           <t>4.3 stars | 6 reviews | Monday: 8:00 AM – 6:00 PM | Tuesday: 8:00 AM – 6:00 PM | Wednesday: 8:00 AM – 6:00 PM | https://maps.google.com/?cid=8109246463616847009&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -4085,39 +4094,39 @@
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="5" t="inlineStr"/>
-      <c r="B63" s="5" t="inlineStr">
+      <c r="A63" s="9" t="inlineStr"/>
+      <c r="B63" s="9" t="inlineStr">
         <is>
           <t>Strand Halal Butchery</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C63" s="9" t="inlineStr">
         <is>
           <t>Food &amp; Hospitality</t>
         </is>
       </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="D63" s="9" t="inlineStr">
         <is>
           <t>Western Cape</t>
         </is>
       </c>
-      <c r="E63" s="5" t="inlineStr">
+      <c r="E63" s="9" t="inlineStr">
         <is>
           <t>Strand</t>
         </is>
       </c>
-      <c r="F63" s="5" t="inlineStr"/>
-      <c r="G63" s="5" t="inlineStr"/>
-      <c r="H63" s="5" t="inlineStr"/>
-      <c r="I63" s="5" t="inlineStr"/>
-      <c r="J63" s="5" t="inlineStr"/>
-      <c r="K63" s="5" t="inlineStr"/>
-      <c r="L63" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M63" s="5" t="inlineStr">
+      <c r="F63" s="9" t="inlineStr"/>
+      <c r="G63" s="9" t="inlineStr"/>
+      <c r="H63" s="9" t="inlineStr"/>
+      <c r="I63" s="9" t="inlineStr"/>
+      <c r="J63" s="9" t="inlineStr"/>
+      <c r="K63" s="9" t="inlineStr"/>
+      <c r="L63" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M63" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -4127,12 +4136,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O63" s="5" t="inlineStr">
+      <c r="O63" s="9" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="P63" s="5" t="inlineStr"/>
+      <c r="P63" s="9" t="inlineStr"/>
       <c r="Q63" s="7" t="inlineStr">
         <is>
           <t>3 stars | 2 reviews | https://maps.google.com/?cid=9540165434278421163&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -4140,43 +4149,43 @@
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="5" t="inlineStr"/>
-      <c r="B64" s="5" t="inlineStr">
+      <c r="A64" s="9" t="inlineStr"/>
+      <c r="B64" s="9" t="inlineStr">
         <is>
           <t>G’s Biltong and Braai</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="C64" s="9" t="inlineStr">
         <is>
           <t>Food &amp; Hospitality</t>
         </is>
       </c>
-      <c r="D64" s="5" t="inlineStr">
+      <c r="D64" s="9" t="inlineStr">
         <is>
           <t>Western Cape</t>
         </is>
       </c>
-      <c r="E64" s="5" t="inlineStr">
+      <c r="E64" s="9" t="inlineStr">
         <is>
           <t>Strand</t>
         </is>
       </c>
-      <c r="F64" s="5" t="inlineStr">
+      <c r="F64" s="9" t="inlineStr">
         <is>
           <t>067 121 8643</t>
         </is>
       </c>
-      <c r="G64" s="5" t="inlineStr"/>
-      <c r="H64" s="5" t="inlineStr"/>
-      <c r="I64" s="5" t="inlineStr"/>
-      <c r="J64" s="5" t="inlineStr"/>
-      <c r="K64" s="5" t="inlineStr"/>
-      <c r="L64" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M64" s="5" t="inlineStr">
+      <c r="G64" s="9" t="inlineStr"/>
+      <c r="H64" s="9" t="inlineStr"/>
+      <c r="I64" s="9" t="inlineStr"/>
+      <c r="J64" s="9" t="inlineStr"/>
+      <c r="K64" s="9" t="inlineStr"/>
+      <c r="L64" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M64" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -4186,12 +4195,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O64" s="5" t="inlineStr">
+      <c r="O64" s="9" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="P64" s="5" t="inlineStr"/>
+      <c r="P64" s="9" t="inlineStr"/>
       <c r="Q64" s="7" t="inlineStr">
         <is>
           <t>4.7 stars | 78 reviews | Monday: 8:30 AM – 5:30 PM | Tuesday: 8:30 AM – 5:30 PM | Wednesday: 8:30 AM – 5:30 PM | https://maps.google.com/?cid=16866996133065796829&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -4199,43 +4208,43 @@
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="5" t="inlineStr"/>
-      <c r="B65" s="5" t="inlineStr">
+      <c r="A65" s="9" t="inlineStr"/>
+      <c r="B65" s="9" t="inlineStr">
         <is>
           <t>M.Y. Biltong &amp; Braai</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C65" s="9" t="inlineStr">
         <is>
           <t>Food &amp; Hospitality</t>
         </is>
       </c>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="D65" s="9" t="inlineStr">
         <is>
           <t>Western Cape</t>
         </is>
       </c>
-      <c r="E65" s="5" t="inlineStr">
+      <c r="E65" s="9" t="inlineStr">
         <is>
           <t>Strand</t>
         </is>
       </c>
-      <c r="F65" s="5" t="inlineStr">
+      <c r="F65" s="9" t="inlineStr">
         <is>
           <t>082 678 1720</t>
         </is>
       </c>
-      <c r="G65" s="5" t="inlineStr"/>
-      <c r="H65" s="5" t="inlineStr"/>
-      <c r="I65" s="5" t="inlineStr"/>
-      <c r="J65" s="5" t="inlineStr"/>
-      <c r="K65" s="5" t="inlineStr"/>
-      <c r="L65" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M65" s="5" t="inlineStr">
+      <c r="G65" s="9" t="inlineStr"/>
+      <c r="H65" s="9" t="inlineStr"/>
+      <c r="I65" s="9" t="inlineStr"/>
+      <c r="J65" s="9" t="inlineStr"/>
+      <c r="K65" s="9" t="inlineStr"/>
+      <c r="L65" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M65" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -4245,12 +4254,12 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O65" s="5" t="inlineStr">
+      <c r="O65" s="9" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="P65" s="5" t="inlineStr"/>
+      <c r="P65" s="9" t="inlineStr"/>
       <c r="Q65" s="7" t="inlineStr">
         <is>
           <t>4.5 stars | 56 reviews | Monday: 8:00 AM – 5:30 PM | Tuesday: 8:00 AM – 5:30 PM | Wednesday: 8:00 AM – 5:30 PM | https://maps.google.com/?cid=13692482145099582452&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
@@ -4258,43 +4267,43 @@
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="5" t="inlineStr"/>
-      <c r="B66" s="5" t="inlineStr">
+      <c r="A66" s="9" t="inlineStr"/>
+      <c r="B66" s="9" t="inlineStr">
         <is>
           <t>Hectic Biltong</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
+      <c r="C66" s="9" t="inlineStr">
         <is>
           <t>Food &amp; Hospitality</t>
         </is>
       </c>
-      <c r="D66" s="5" t="inlineStr">
+      <c r="D66" s="9" t="inlineStr">
         <is>
           <t>Western Cape</t>
         </is>
       </c>
-      <c r="E66" s="5" t="inlineStr">
+      <c r="E66" s="9" t="inlineStr">
         <is>
           <t>Strand</t>
         </is>
       </c>
-      <c r="F66" s="5" t="inlineStr">
+      <c r="F66" s="9" t="inlineStr">
         <is>
           <t>021 854 8603</t>
         </is>
       </c>
-      <c r="G66" s="5" t="inlineStr"/>
-      <c r="H66" s="5" t="inlineStr"/>
-      <c r="I66" s="5" t="inlineStr"/>
-      <c r="J66" s="5" t="inlineStr"/>
-      <c r="K66" s="5" t="inlineStr"/>
-      <c r="L66" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M66" s="5" t="inlineStr">
+      <c r="G66" s="9" t="inlineStr"/>
+      <c r="H66" s="9" t="inlineStr"/>
+      <c r="I66" s="9" t="inlineStr"/>
+      <c r="J66" s="9" t="inlineStr"/>
+      <c r="K66" s="9" t="inlineStr"/>
+      <c r="L66" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M66" s="9" t="inlineStr">
         <is>
           <t>Google Maps</t>
         </is>
@@ -4304,17 +4313,604 @@
           <t>New Lead</t>
         </is>
       </c>
-      <c r="O66" s="5" t="inlineStr">
+      <c r="O66" s="9" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="P66" s="5" t="inlineStr"/>
+      <c r="P66" s="9" t="inlineStr"/>
       <c r="Q66" s="7" t="inlineStr">
         <is>
           <t>4.7 stars | 27 reviews | Monday: 8:30 AM – 6:00 PM | Tuesday: 8:30 AM – 6:00 PM | Wednesday: 8:30 AM – 6:00 PM | https://maps.google.com/?cid=15072989852552512999&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
         </is>
       </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="inlineStr"/>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>Kallos House of Beauty</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>Beauty &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>Western Cape</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>Bellville</t>
+        </is>
+      </c>
+      <c r="F67" s="9" t="inlineStr">
+        <is>
+          <t>067 580 3489</t>
+        </is>
+      </c>
+      <c r="G67" s="9" t="inlineStr"/>
+      <c r="H67" s="9" t="inlineStr"/>
+      <c r="I67" s="9" t="inlineStr">
+        <is>
+          <t>https://maps.google.com/?cid=4722251476358147844&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+        </is>
+      </c>
+      <c r="J67" s="9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K67" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="L67" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M67" s="9" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="N67" s="9" t="inlineStr">
+        <is>
+          <t>New Lead</t>
+        </is>
+      </c>
+      <c r="O67" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="P67" s="9" t="inlineStr"/>
+      <c r="Q67" s="7" t="inlineStr">
+        <is>
+          <t>Monday: 9:00 AM – 6:00 PM | Tuesday: 9:00 AM – 6:00 PM | Wednesday: 9:00 AM – 6:00 PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="inlineStr"/>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>Salon Di Belle Nails &amp; Beauty</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>Beauty &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>Western Cape</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>Bellville</t>
+        </is>
+      </c>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>083 976 9841</t>
+        </is>
+      </c>
+      <c r="G68" s="9" t="inlineStr"/>
+      <c r="H68" s="9" t="inlineStr"/>
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>https://maps.google.com/?cid=509855459896604258&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+        </is>
+      </c>
+      <c r="J68" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K68" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="L68" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M68" s="9" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="N68" s="9" t="inlineStr">
+        <is>
+          <t>New Lead</t>
+        </is>
+      </c>
+      <c r="O68" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="P68" s="9" t="inlineStr"/>
+      <c r="Q68" s="7" t="inlineStr">
+        <is>
+          <t>Monday: Closed | Tuesday: 8:00 AM – 5:00 PM | Wednesday: 8:00 AM – 5:00 PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="inlineStr"/>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>Tanganyika Hair Salon</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>Beauty &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>Western Cape</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>Bellville</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="inlineStr">
+        <is>
+          <t>068 410 9871</t>
+        </is>
+      </c>
+      <c r="G69" s="9" t="inlineStr"/>
+      <c r="H69" s="9" t="inlineStr"/>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>https://maps.google.com/?cid=1425191478846833502&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+        </is>
+      </c>
+      <c r="J69" s="9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K69" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="L69" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M69" s="9" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="N69" s="9" t="inlineStr">
+        <is>
+          <t>New Lead</t>
+        </is>
+      </c>
+      <c r="O69" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="P69" s="9" t="inlineStr"/>
+      <c r="Q69" s="7" t="inlineStr">
+        <is>
+          <t>Monday: 8:00 AM – 9:00 PM | Tuesday: 8:00 AM – 9:00 PM | Wednesday: 8:00 AM – 9:00 PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="inlineStr"/>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>Lynne Hair Beauty</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>Beauty &amp; Wellness</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>Western Cape</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t>Bellville</t>
+        </is>
+      </c>
+      <c r="F70" s="9" t="inlineStr">
+        <is>
+          <t>082 871 8385</t>
+        </is>
+      </c>
+      <c r="G70" s="9" t="inlineStr"/>
+      <c r="H70" s="9" t="inlineStr"/>
+      <c r="I70" s="9" t="inlineStr">
+        <is>
+          <t>https://maps.google.com/?cid=11414757215570970640&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+        </is>
+      </c>
+      <c r="J70" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K70" s="9" t="n">
+        <v>106</v>
+      </c>
+      <c r="L70" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M70" s="9" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="N70" s="9" t="inlineStr">
+        <is>
+          <t>New Lead</t>
+        </is>
+      </c>
+      <c r="O70" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="P70" s="9" t="inlineStr"/>
+      <c r="Q70" s="7" t="inlineStr">
+        <is>
+          <t>Monday: Closed | Tuesday: 8:00 AM – 7:00 PM | Wednesday: 8:00 AM – 7:00 PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr"/>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>Marks Paints Parow</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>Trades &amp; Home Services</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>Western Cape</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
+          <t>Parow</t>
+        </is>
+      </c>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>021 933 3770</t>
+        </is>
+      </c>
+      <c r="G71" s="9" t="inlineStr"/>
+      <c r="H71" s="9" t="inlineStr"/>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>https://maps.google.com/?cid=18267912139789332266&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+        </is>
+      </c>
+      <c r="J71" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K71" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="L71" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M71" s="9" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="N71" s="9" t="inlineStr">
+        <is>
+          <t>New Lead</t>
+        </is>
+      </c>
+      <c r="O71" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="P71" s="9" t="inlineStr"/>
+      <c r="Q71" s="7" t="inlineStr">
+        <is>
+          <t>Monday: 8:00 AM – 4:00 PM | Tuesday: 8:00 AM – 4:00 PM | Wednesday: 8:00 AM – 4:00 PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="inlineStr"/>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>Painters for you at affordable price</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>Trades &amp; Home Services</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>Western Cape</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>Parow</t>
+        </is>
+      </c>
+      <c r="F72" s="9" t="inlineStr">
+        <is>
+          <t>072 232 4743</t>
+        </is>
+      </c>
+      <c r="G72" s="9" t="inlineStr"/>
+      <c r="H72" s="9" t="inlineStr"/>
+      <c r="I72" s="9" t="inlineStr">
+        <is>
+          <t>https://maps.google.com/?cid=2735857892439108176&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+        </is>
+      </c>
+      <c r="J72" s="9" t="inlineStr"/>
+      <c r="K72" s="9" t="inlineStr"/>
+      <c r="L72" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M72" s="9" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="N72" s="9" t="inlineStr">
+        <is>
+          <t>New Lead</t>
+        </is>
+      </c>
+      <c r="O72" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="P72" s="9" t="inlineStr"/>
+      <c r="Q72" s="7" t="inlineStr">
+        <is>
+          <t>Monday: Open 24 hours | Tuesday: Open 24 hours | Wednesday: Open 24 hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="inlineStr"/>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>Richard Tiling Painting and Renovation</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>Trades &amp; Home Services</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>Western Cape</t>
+        </is>
+      </c>
+      <c r="E73" s="9" t="inlineStr">
+        <is>
+          <t>Parow</t>
+        </is>
+      </c>
+      <c r="F73" s="9" t="inlineStr"/>
+      <c r="G73" s="9" t="inlineStr"/>
+      <c r="H73" s="9" t="inlineStr"/>
+      <c r="I73" s="9" t="inlineStr">
+        <is>
+          <t>https://maps.google.com/?cid=9298098938482728964&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+        </is>
+      </c>
+      <c r="J73" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K73" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L73" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M73" s="9" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="N73" s="9" t="inlineStr">
+        <is>
+          <t>New Lead</t>
+        </is>
+      </c>
+      <c r="O73" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="P73" s="9" t="inlineStr"/>
+      <c r="Q73" s="7" t="inlineStr">
+        <is>
+          <t>Monday: 8:00 AM – 5:00 PM | Tuesday: 8:00 AM – 5:00 PM | Wednesday: 8:00 AM – 5:00 PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="inlineStr"/>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>Parow Panel Beaters</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>Trades &amp; Home Services</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>Western Cape</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>Parow</t>
+        </is>
+      </c>
+      <c r="F74" s="9" t="inlineStr">
+        <is>
+          <t>069 284 9560</t>
+        </is>
+      </c>
+      <c r="G74" s="9" t="inlineStr"/>
+      <c r="H74" s="9" t="inlineStr"/>
+      <c r="I74" s="9" t="inlineStr">
+        <is>
+          <t>https://maps.google.com/?cid=2624487371780644938&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+        </is>
+      </c>
+      <c r="J74" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K74" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="L74" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M74" s="9" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="N74" s="9" t="inlineStr">
+        <is>
+          <t>New Lead</t>
+        </is>
+      </c>
+      <c r="O74" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="P74" s="9" t="inlineStr"/>
+      <c r="Q74" s="7" t="inlineStr">
+        <is>
+          <t>Monday: 8:00 AM – 5:30 PM | Tuesday: 8:00 AM – 5:30 PM | Wednesday: 8:00 AM – 5:30 PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr"/>
+      <c r="B75" s="10" t="inlineStr">
+        <is>
+          <t>Mary's Language Tutoring</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>Professional Services</t>
+        </is>
+      </c>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>Western Cape</t>
+        </is>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>Fish Hoek</t>
+        </is>
+      </c>
+      <c r="F75" s="10" t="inlineStr"/>
+      <c r="G75" s="10" t="inlineStr"/>
+      <c r="H75" s="10" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/maryenglishtutor/</t>
+        </is>
+      </c>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
+          <t>https://maps.google.com/?cid=9406334021162778714&amp;g_mp=Cidnb29nbGUubWFwcy5wbGFjZXMudjEuUGxhY2VzLlNlYXJjaFRleHQQAhgEIAA</t>
+        </is>
+      </c>
+      <c r="J75" s="10" t="inlineStr"/>
+      <c r="K75" s="10" t="inlineStr"/>
+      <c r="L75" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M75" s="10" t="inlineStr">
+        <is>
+          <t>Google Maps</t>
+        </is>
+      </c>
+      <c r="N75" s="10" t="inlineStr">
+        <is>
+          <t>New Lead</t>
+        </is>
+      </c>
+      <c r="O75" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="P75" s="10" t="inlineStr"/>
+      <c r="Q75" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
